--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{046DE1DD-8AE6-4F1A-966D-0840DADC2859}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A65329-72D2-429A-A131-7D2081412124}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -3571,6 +3571,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -6619,6 +6620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6703,7 +6705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -6773,7 +6775,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -6843,7 +6845,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -6913,7 +6915,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -6983,7 +6985,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -7053,7 +7055,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -7123,7 +7125,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -7193,7 +7195,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -7263,7 +7265,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -7333,7 +7335,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -7403,7 +7405,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -7473,7 +7475,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -7543,7 +7545,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -7610,7 +7612,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -7679,7 +7681,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -7748,7 +7750,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -7817,7 +7819,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -7886,7 +7888,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -7947,7 +7949,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -8016,7 +8018,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -8085,7 +8087,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -8155,7 +8157,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -8225,7 +8227,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -8292,7 +8294,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -8356,7 +8358,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -8416,7 +8418,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -8479,7 +8481,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -8544,7 +8546,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -8606,7 +8608,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -8664,7 +8666,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -8722,7 +8724,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -8796,7 +8798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -8870,7 +8872,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -8944,7 +8946,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -9018,7 +9020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -9092,7 +9094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -9166,7 +9168,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -9240,7 +9242,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -9304,7 +9306,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -9378,7 +9380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -9452,7 +9454,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -9526,7 +9528,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -9600,7 +9602,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -9674,7 +9676,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -9748,7 +9750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -9822,7 +9824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -9896,7 +9898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -9968,7 +9970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -10042,7 +10044,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -10116,7 +10118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -10176,7 +10178,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -10250,7 +10252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -10324,7 +10326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -10398,7 +10400,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -10470,7 +10472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -10544,7 +10546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -10618,7 +10620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -10690,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -10764,7 +10766,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -10838,7 +10840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -10912,7 +10914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -10986,7 +10988,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -11060,7 +11062,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -11134,7 +11136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -11206,7 +11208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -11280,7 +11282,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -11350,7 +11352,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -11424,7 +11426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -11494,7 +11496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -11564,7 +11566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -11638,7 +11640,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -11710,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -11784,7 +11786,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -11858,7 +11860,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -11932,7 +11934,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -12006,7 +12008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -12080,7 +12082,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -12154,7 +12156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -12211,7 +12213,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -12267,7 +12269,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -12335,7 +12337,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -12397,7 +12399,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -12471,7 +12473,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -12545,7 +12547,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -12619,7 +12621,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -12693,7 +12695,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -12767,7 +12769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -12841,7 +12843,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -12903,7 +12905,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -12962,7 +12964,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -13020,7 +13022,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -13078,7 +13080,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -13138,7 +13140,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -13194,7 +13196,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -13252,7 +13254,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -13310,7 +13312,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -13366,7 +13368,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -13424,7 +13426,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -13482,7 +13484,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -13540,7 +13542,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -13598,7 +13600,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -13656,7 +13658,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -13712,7 +13714,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -13768,7 +13770,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -13824,7 +13826,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -13882,7 +13884,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -13940,7 +13942,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -13998,7 +14000,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -14054,7 +14056,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -14110,7 +14112,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -14166,7 +14168,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -14222,7 +14224,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -14278,7 +14280,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -14334,7 +14336,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -14446,7 +14448,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -14502,7 +14504,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -14558,7 +14560,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -14612,7 +14614,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -14668,7 +14670,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -14724,7 +14726,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -14780,7 +14782,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -14836,7 +14838,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -14892,7 +14894,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -14948,7 +14950,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -15004,7 +15006,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -15058,7 +15060,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -15110,7 +15112,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -15165,7 +15167,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -15219,7 +15221,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>542</v>
       </c>
@@ -15283,7 +15285,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>542</v>
       </c>
@@ -15357,7 +15359,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -15431,7 +15433,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -15505,7 +15507,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -15579,7 +15581,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -15641,7 +15643,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -15712,7 +15714,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -15783,7 +15785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -15854,7 +15856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -15908,7 +15910,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -15962,7 +15964,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -16016,7 +16018,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -16070,7 +16072,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -16143,7 +16145,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -16217,7 +16219,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -16291,7 +16293,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -16365,7 +16367,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -16439,7 +16441,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -16513,7 +16515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -16587,7 +16589,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -16661,7 +16663,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -16735,7 +16737,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -16809,7 +16811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -16886,7 +16888,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -16963,7 +16965,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>122</v>
       </c>
@@ -17040,7 +17042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -17117,7 +17119,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -17194,7 +17196,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -17271,7 +17273,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -17348,7 +17350,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -17425,7 +17427,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -17502,7 +17504,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -17579,7 +17581,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -17656,7 +17658,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -17733,7 +17735,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -17810,7 +17812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -17887,7 +17889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -17964,7 +17966,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -18041,7 +18043,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -18118,7 +18120,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -18195,7 +18197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -18272,7 +18274,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -18349,7 +18351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -18426,7 +18428,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -18503,7 +18505,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -18580,7 +18582,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -18657,7 +18659,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -18734,7 +18736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -18811,7 +18813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -18888,7 +18890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -18965,7 +18967,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -19042,7 +19044,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -19119,7 +19121,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -19196,7 +19198,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -19273,7 +19275,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -19350,7 +19352,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -19427,7 +19429,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -19504,7 +19506,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -19579,7 +19581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -19656,7 +19658,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -19731,7 +19733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -19808,7 +19810,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -19885,7 +19887,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -19962,7 +19964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -20039,7 +20041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>239</v>
       </c>
@@ -20116,7 +20118,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>239</v>
       </c>
@@ -20193,7 +20195,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -20270,7 +20272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>239</v>
       </c>
@@ -20345,7 +20347,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>239</v>
       </c>
@@ -20422,7 +20424,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>239</v>
       </c>
@@ -20499,7 +20501,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>241</v>
       </c>
@@ -20568,7 +20570,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>434</v>
       </c>
@@ -20643,7 +20645,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -20720,7 +20722,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -20797,7 +20799,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -20874,7 +20876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -20951,7 +20953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -21028,7 +21030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -21105,7 +21107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -21182,7 +21184,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -21259,7 +21261,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -21336,7 +21338,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -21409,7 +21411,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -21481,7 +21483,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -21555,7 +21557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -21629,7 +21631,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -21703,7 +21705,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -21777,7 +21779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -21851,7 +21853,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -21925,7 +21927,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -21999,7 +22001,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -22073,7 +22075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -22148,7 +22150,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -22222,7 +22224,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -22296,7 +22298,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -22370,7 +22372,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -22444,7 +22446,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -22518,7 +22520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -22592,7 +22594,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -22666,7 +22668,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -22740,7 +22742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -22814,7 +22816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>509</v>
       </c>
@@ -22875,7 +22877,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>509</v>
       </c>
@@ -22949,7 +22951,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -23023,7 +23025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -23097,7 +23099,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -23171,7 +23173,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -23245,7 +23247,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -23319,7 +23321,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -23393,7 +23395,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -23467,7 +23469,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -23541,7 +23543,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -23615,7 +23617,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -23689,7 +23691,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -23763,7 +23765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -23837,7 +23839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -23911,7 +23913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -23985,7 +23987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -24059,7 +24061,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -24133,7 +24135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -24207,7 +24209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -24282,7 +24284,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -24359,7 +24361,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -24436,7 +24438,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -24513,7 +24515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -24590,7 +24592,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>143</v>
       </c>
@@ -24667,7 +24669,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -24744,7 +24746,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -24821,7 +24823,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -24898,7 +24900,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -24948,7 +24950,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -25019,7 +25021,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -25084,7 +25086,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -25153,7 +25155,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -25230,7 +25232,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -25307,7 +25309,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -25384,7 +25386,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -25461,7 +25463,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -25526,7 +25528,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -25591,7 +25593,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -25656,7 +25658,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>215</v>
       </c>
@@ -25733,7 +25735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -25810,7 +25812,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -25887,7 +25889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -25964,7 +25966,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -26041,7 +26043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -26118,7 +26120,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -26195,7 +26197,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>219</v>
       </c>
@@ -26270,7 +26272,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -26347,7 +26349,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -26424,7 +26426,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -26501,7 +26503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -26578,7 +26580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -26655,7 +26657,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -26732,7 +26734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -26790,7 +26792,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>220</v>
       </c>
@@ -26865,7 +26867,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -26942,7 +26944,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -27019,7 +27021,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -27096,7 +27098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -27173,7 +27175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -27246,7 +27248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -27323,7 +27325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -27386,7 +27388,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -27449,7 +27451,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -27512,7 +27514,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -27577,7 +27579,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -27640,7 +27642,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -27705,7 +27707,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -27768,7 +27770,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -27833,7 +27835,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -27898,7 +27900,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -27961,7 +27963,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>268</v>
       </c>
@@ -28026,7 +28028,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>269</v>
       </c>
@@ -28091,7 +28093,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>270</v>
       </c>
@@ -28156,7 +28158,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>271</v>
       </c>
@@ -28221,7 +28223,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -28286,7 +28288,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -28363,7 +28365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -28440,7 +28442,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -28517,7 +28519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -28594,7 +28596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -28671,7 +28673,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -28748,7 +28750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -28825,7 +28827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -28902,7 +28904,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -28979,7 +28981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -29044,7 +29046,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -29109,7 +29111,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>278</v>
       </c>
@@ -29186,7 +29188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>278</v>
       </c>
@@ -29263,7 +29265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -29340,7 +29342,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -29417,7 +29419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -29482,7 +29484,7 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
     </row>
-    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -29547,7 +29549,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -29612,7 +29614,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>286</v>
       </c>
@@ -29689,7 +29691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>286</v>
       </c>
@@ -29766,7 +29768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -29843,7 +29845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -29920,7 +29922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -29997,7 +29999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -30074,7 +30076,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -30151,7 +30153,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -30228,7 +30230,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -30305,7 +30307,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>294</v>
       </c>
@@ -30382,7 +30384,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -30459,7 +30461,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -30536,7 +30538,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -30613,7 +30615,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>302</v>
       </c>
@@ -30690,7 +30692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>302</v>
       </c>
@@ -30767,7 +30769,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -30844,7 +30846,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -30921,7 +30923,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -30998,7 +31000,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -31073,7 +31075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -31150,7 +31152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -31227,7 +31229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -31304,7 +31306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -31369,7 +31371,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -31434,7 +31436,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -31499,7 +31501,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>325</v>
       </c>
@@ -31564,7 +31566,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>327</v>
       </c>
@@ -31629,7 +31631,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -31694,7 +31696,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>337</v>
       </c>
@@ -31759,7 +31761,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>338</v>
       </c>
@@ -31824,7 +31826,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -31889,7 +31891,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -31954,7 +31956,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -32019,7 +32021,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>357</v>
       </c>
@@ -32080,7 +32082,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -32145,7 +32147,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -32206,7 +32208,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -32283,7 +32285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -32360,7 +32362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -32437,7 +32439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -32500,7 +32502,7 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>364</v>
       </c>
@@ -32565,7 +32567,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -32642,7 +32644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -32719,7 +32721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -32796,7 +32798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -32861,7 +32863,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -32938,7 +32940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -33015,7 +33017,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -33092,7 +33094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -33157,7 +33159,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -33222,7 +33224,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -33287,7 +33289,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -33352,7 +33354,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -33417,7 +33419,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -33482,7 +33484,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -33547,7 +33549,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -33624,7 +33626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -33701,7 +33703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -33778,7 +33780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -33855,7 +33857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -33928,7 +33930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -34002,7 +34004,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -34076,7 +34078,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -34150,7 +34152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -34224,7 +34226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -34298,7 +34300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -34372,7 +34374,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -34446,7 +34448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -34520,7 +34522,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -34594,7 +34596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -34668,7 +34670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -34742,7 +34744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -34816,7 +34818,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -34881,7 +34883,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -34946,7 +34948,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -35011,7 +35013,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -35076,7 +35078,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -35141,7 +35143,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -35206,7 +35208,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -35283,7 +35285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -35360,7 +35362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -35437,7 +35439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -35514,7 +35516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -35579,7 +35581,7 @@
       <c r="X409" s="3"/>
       <c r="Y409" s="3"/>
     </row>
-    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -35638,7 +35640,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -35715,7 +35717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -35792,7 +35794,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -35869,7 +35871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -35946,7 +35948,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -36023,7 +36025,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -36096,7 +36098,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -36173,7 +36175,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -36250,7 +36252,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -36327,7 +36329,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -36404,7 +36406,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -36479,7 +36481,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -36556,7 +36558,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -36629,7 +36631,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -36704,7 +36706,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -36758,7 +36760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -36835,7 +36837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -36912,7 +36914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -36989,7 +36991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -37066,7 +37068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -37143,7 +37145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -37220,7 +37222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -37297,7 +37299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -37374,7 +37376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -37451,7 +37453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -37528,7 +37530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -37605,7 +37607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -37682,7 +37684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>433</v>
       </c>
@@ -37759,7 +37761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -37836,7 +37838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -37913,7 +37915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -37990,7 +37992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -38063,7 +38065,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -38134,7 +38136,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -38209,7 +38211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -38267,7 +38269,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>435</v>
       </c>
@@ -38342,7 +38344,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -38419,7 +38421,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -38496,7 +38498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -38573,7 +38575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -38650,7 +38652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -38727,7 +38729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -38804,7 +38806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -38881,7 +38883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -38958,7 +38960,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -39035,7 +39037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -39112,7 +39114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -39189,7 +39191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -39266,7 +39268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -39325,7 +39327,7 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -39386,7 +39388,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -39447,7 +39449,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -39508,7 +39510,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -39569,7 +39571,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -39626,7 +39628,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -39687,7 +39689,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -39748,7 +39750,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -39809,7 +39811,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -39886,7 +39888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -39963,7 +39965,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -40040,7 +40042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -40117,7 +40119,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -40190,7 +40192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -40264,7 +40266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -40338,7 +40340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -40412,7 +40414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -40486,7 +40488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -40560,7 +40562,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -40634,7 +40636,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -40708,7 +40710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -40782,7 +40784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -40856,7 +40858,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -40930,7 +40932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -41004,7 +41006,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -41078,7 +41080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -41139,7 +41141,7 @@
       <c r="X485" s="3"/>
       <c r="Y485" s="3"/>
     </row>
-    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -41216,7 +41218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -41293,7 +41295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -41370,7 +41372,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -41447,7 +41449,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -41518,7 +41520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -41592,7 +41594,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -41666,7 +41668,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -41740,7 +41742,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -41814,7 +41816,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -41888,7 +41890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -41962,7 +41964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -42036,7 +42038,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -42110,7 +42112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -42184,7 +42186,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -42258,7 +42260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -42332,7 +42334,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -42406,7 +42408,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -42479,7 +42481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -42553,7 +42555,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -42627,7 +42629,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -42701,7 +42703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -42775,7 +42777,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -42849,7 +42851,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -42923,7 +42925,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -42997,7 +42999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -43071,7 +43073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -43145,7 +43147,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -43219,7 +43221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -43293,7 +43295,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -43367,7 +43369,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -43440,7 +43442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -43517,7 +43519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -43594,7 +43596,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -43671,7 +43673,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -43748,7 +43750,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -43825,7 +43827,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -43902,7 +43904,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -43979,7 +43981,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -44056,7 +44058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -44133,7 +44135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -44210,7 +44212,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -44287,7 +44289,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -44364,7 +44366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -44437,7 +44439,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -44514,7 +44516,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -44591,7 +44593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -44668,7 +44670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -44745,7 +44747,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -44822,7 +44824,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -44899,7 +44901,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -44976,7 +44978,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -45053,7 +45055,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -45130,7 +45132,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -45207,7 +45209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -45284,7 +45286,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -45361,7 +45363,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -45422,7 +45424,7 @@
       <c r="X542" s="3"/>
       <c r="Y542" s="3"/>
     </row>
-    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -45492,7 +45494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -45551,7 +45553,7 @@
       <c r="X544" s="3"/>
       <c r="Y544" s="3"/>
     </row>
-    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -45610,7 +45612,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -45669,7 +45671,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>514</v>
       </c>
@@ -45726,7 +45728,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -45781,7 +45783,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -45836,7 +45838,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -45913,7 +45915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -45990,7 +45992,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -46067,7 +46069,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -46144,7 +46146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -46221,7 +46223,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -46298,7 +46300,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -46375,7 +46377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -46452,7 +46454,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -46529,7 +46531,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -46606,7 +46608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -46683,7 +46685,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -46760,7 +46762,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -46837,7 +46839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -46914,7 +46916,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -46969,7 +46971,7 @@
       <c r="X564" s="3"/>
       <c r="Y564" s="3"/>
     </row>
-    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -47024,7 +47026,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -47093,7 +47095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -47170,7 +47172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -47247,7 +47249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -47324,7 +47326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -47401,7 +47403,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -47478,7 +47480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -47555,7 +47557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -47632,7 +47634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -47709,7 +47711,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -47786,7 +47788,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -47863,7 +47865,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -47940,7 +47942,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -48017,7 +48019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -48094,7 +48096,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -48171,7 +48173,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -48248,7 +48250,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -48325,7 +48327,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -48382,7 +48384,7 @@
       <c r="X583" s="3"/>
       <c r="Y583" s="3"/>
     </row>
-    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -48437,7 +48439,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -48492,7 +48494,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -48549,7 +48551,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -48624,7 +48626,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -48701,7 +48703,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -48778,7 +48780,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -48853,7 +48855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -48930,7 +48932,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -49007,7 +49009,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -49084,7 +49086,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -49161,7 +49163,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -49218,7 +49220,7 @@
       <c r="X595" s="3"/>
       <c r="Y595" s="3"/>
     </row>
-    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -49275,7 +49277,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -49330,7 +49332,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -49385,7 +49387,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -49462,7 +49464,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -49539,7 +49541,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -49616,7 +49618,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -49693,7 +49695,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -49770,7 +49772,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -49847,7 +49849,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -49924,7 +49926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -50001,7 +50003,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -50078,7 +50080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -50155,7 +50157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -50232,7 +50234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -50309,7 +50311,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -50384,7 +50386,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -50459,7 +50461,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>238</v>
       </c>
@@ -50532,7 +50534,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -50609,7 +50611,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -50686,7 +50688,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -50763,7 +50765,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -50840,7 +50842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -50917,7 +50919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -50994,7 +50996,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -51071,7 +51073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -51148,7 +51150,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>240</v>
       </c>
@@ -51223,7 +51225,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -51298,7 +51300,7 @@
       </c>
       <c r="Y623" s="3"/>
     </row>
-    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -51354,7 +51356,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -51431,7 +51433,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -51508,7 +51510,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>266</v>
       </c>
@@ -51585,7 +51587,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -51662,7 +51664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -51739,7 +51741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -51814,7 +51816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -51891,7 +51893,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -51968,7 +51970,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -52045,7 +52047,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -52122,7 +52124,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -52199,7 +52201,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -52276,7 +52278,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -52353,7 +52355,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -52430,7 +52432,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -52505,7 +52507,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -52580,7 +52582,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -52653,7 +52655,7 @@
       <c r="X641" s="3"/>
       <c r="Y641" s="3"/>
     </row>
-    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -52726,7 +52728,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -52803,7 +52805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -52880,7 +52882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -52957,7 +52959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -53034,7 +53036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -53111,7 +53113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -53188,7 +53190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -53265,7 +53267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -53342,7 +53344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -53419,7 +53421,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -53496,7 +53498,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -53573,7 +53575,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -53650,7 +53652,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -53727,7 +53729,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -53804,7 +53806,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -53881,7 +53883,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -53958,7 +53960,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -54035,7 +54037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -54112,7 +54114,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -54189,7 +54191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -54266,7 +54268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -54343,7 +54345,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -54418,7 +54420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -54489,7 +54491,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -54566,7 +54568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -54643,7 +54645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -54720,7 +54722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -54797,7 +54799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -54874,7 +54876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -54951,7 +54953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -55028,7 +55030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -55105,7 +55107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -55182,7 +55184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -55259,7 +55261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -55336,7 +55338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -55413,7 +55415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -55490,7 +55492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -55567,7 +55569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -55644,7 +55646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -55721,7 +55723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -55798,7 +55800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -55875,7 +55877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -55952,7 +55954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -56029,7 +56031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -56106,7 +56108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -56183,7 +56185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -56260,7 +56262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -56337,7 +56339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -56414,7 +56416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -56491,7 +56493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -56568,7 +56570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -56645,7 +56647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -56722,7 +56724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -56799,7 +56801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -56876,7 +56878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -56953,7 +56955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -57030,7 +57032,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -57107,7 +57109,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -57184,7 +57186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -57261,7 +57263,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -57338,7 +57340,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -57415,7 +57417,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -57492,7 +57494,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -57569,7 +57571,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -57646,7 +57648,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -57723,7 +57725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -57800,7 +57802,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -57877,7 +57879,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -57954,7 +57956,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -58029,7 +58031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -58106,7 +58108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -58183,7 +58185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -58260,7 +58262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -58337,7 +58339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -58414,7 +58416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -58491,7 +58493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -58568,7 +58570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -58645,7 +58647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -58722,7 +58724,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -58799,7 +58801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -58876,7 +58878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -58953,7 +58955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -59026,7 +59028,7 @@
       <c r="X724" s="3"/>
       <c r="Y724" s="3"/>
     </row>
-    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -59103,7 +59105,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -59180,7 +59182,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -59257,7 +59259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -59334,7 +59336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -59411,7 +59413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -59488,7 +59490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -59565,7 +59567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -59642,7 +59644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -59719,7 +59721,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -59796,7 +59798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -59865,7 +59867,7 @@
       <c r="X735" s="3"/>
       <c r="Y735" s="3"/>
     </row>
-    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -59930,7 +59932,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -60001,7 +60003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -60078,7 +60080,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -60155,7 +60157,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -60232,7 +60234,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -60303,7 +60305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -60380,7 +60382,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -60457,7 +60459,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -60534,7 +60536,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -60609,7 +60611,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -60686,7 +60688,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -60763,7 +60765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -60840,7 +60842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -60917,7 +60919,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -60994,7 +60996,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -61071,7 +61073,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -61148,7 +61150,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -61225,7 +61227,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -61302,7 +61304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -61379,7 +61381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -61456,7 +61458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -61531,7 +61533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -61608,7 +61610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -61685,7 +61687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -61762,7 +61764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -61839,7 +61841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -61916,7 +61918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -61993,7 +61995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -62070,7 +62072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -62147,7 +62149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -62224,7 +62226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -62301,7 +62303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -62378,7 +62380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -62455,7 +62457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -62522,7 +62524,7 @@
       <c r="X770" s="3"/>
       <c r="Y770" s="3"/>
     </row>
-    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -62597,7 +62599,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -62668,7 +62670,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -62743,7 +62745,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -62820,7 +62822,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -62897,7 +62899,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -62974,7 +62976,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -63051,7 +63053,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -63128,7 +63130,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -63205,7 +63207,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -63282,7 +63284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -63343,7 +63345,7 @@
       <c r="X781" s="3"/>
       <c r="Y781" s="3"/>
     </row>
-    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -63397,7 +63399,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -63454,7 +63456,7 @@
       <c r="X783" s="3"/>
       <c r="Y783" s="3"/>
     </row>
-    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -63529,7 +63531,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -63606,7 +63608,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -63685,6 +63687,13 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="495"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
@@ -63858,7 +63867,7 @@
         <v>84</v>
       </c>
       <c r="AA2">
-        <f>IF(A2=A1,0,1)</f>
+        <f t="shared" ref="AA2:AA65" si="0">IF(A2=A1,0,1)</f>
         <v>1</v>
       </c>
     </row>
@@ -63936,7 +63945,7 @@
         <v>85</v>
       </c>
       <c r="AA3">
-        <f>IF(A3=A2,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64014,7 +64023,7 @@
         <v>87</v>
       </c>
       <c r="AA4">
-        <f>IF(A4=A3,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64092,7 +64101,7 @@
         <v>88</v>
       </c>
       <c r="AA5">
-        <f>IF(A5=A4,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64170,7 +64179,7 @@
         <v>89</v>
       </c>
       <c r="AA6">
-        <f>IF(A6=A5,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64248,7 +64257,7 @@
         <v>90</v>
       </c>
       <c r="AA7">
-        <f>IF(A7=A6,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64326,7 +64335,7 @@
         <v>91</v>
       </c>
       <c r="AA8">
-        <f>IF(A8=A7,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64404,7 +64413,7 @@
         <v>92</v>
       </c>
       <c r="AA9">
-        <f>IF(A9=A8,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64482,7 +64491,7 @@
         <v>94</v>
       </c>
       <c r="AA10">
-        <f>IF(A10=A9,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64560,7 +64569,7 @@
         <v>100</v>
       </c>
       <c r="AA11">
-        <f>IF(A11=A10,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64638,7 +64647,7 @@
         <v>104</v>
       </c>
       <c r="AA12">
-        <f>IF(A12=A11,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64716,7 +64725,7 @@
         <v>106</v>
       </c>
       <c r="AA13">
-        <f>IF(A13=A12,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64791,7 +64800,7 @@
         <v>109</v>
       </c>
       <c r="AA14">
-        <f>IF(A14=A13,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64868,7 +64877,7 @@
         <v>112</v>
       </c>
       <c r="AA15">
-        <f>IF(A15=A14,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -64945,7 +64954,7 @@
         <v>113</v>
       </c>
       <c r="AA16">
-        <f>IF(A16=A15,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65022,7 +65031,7 @@
         <v>114</v>
       </c>
       <c r="AA17">
-        <f>IF(A17=A16,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65099,7 +65108,7 @@
         <v>115</v>
       </c>
       <c r="AA18">
-        <f>IF(A18=A17,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65168,7 +65177,7 @@
         <v>116</v>
       </c>
       <c r="AA19">
-        <f>IF(A19=A18,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65245,7 +65254,7 @@
         <v>117</v>
       </c>
       <c r="AA20">
-        <f>IF(A20=A19,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65322,7 +65331,7 @@
         <v>118</v>
       </c>
       <c r="AA21">
-        <f>IF(A21=A20,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65400,7 +65409,7 @@
         <v>126</v>
       </c>
       <c r="AA22">
-        <f>IF(A22=A21,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65478,7 +65487,7 @@
         <v>127</v>
       </c>
       <c r="AA23">
-        <f>IF(A23=A22,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65553,7 +65562,7 @@
         <v>133</v>
       </c>
       <c r="AA24">
-        <f>IF(A24=A23,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65625,7 +65634,7 @@
         <v>144</v>
       </c>
       <c r="AA25">
-        <f>IF(A25=A24,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65693,7 +65702,7 @@
         <v>147</v>
       </c>
       <c r="AA26">
-        <f>IF(A26=A25,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65764,7 +65773,7 @@
         <v>150</v>
       </c>
       <c r="AA27">
-        <f>IF(A27=A26,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65837,7 +65846,7 @@
         <v>151</v>
       </c>
       <c r="AA28">
-        <f>IF(A28=A27,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65907,7 +65916,7 @@
         <v>200</v>
       </c>
       <c r="AA29">
-        <f>IF(A29=A28,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -65973,7 +65982,7 @@
         <v>202</v>
       </c>
       <c r="AA30">
-        <f>IF(A30=A29,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66039,7 +66048,7 @@
         <v>206</v>
       </c>
       <c r="AA31">
-        <f>IF(A31=A30,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66121,7 +66130,7 @@
         <v>216</v>
       </c>
       <c r="AA32">
-        <f>IF(A32=A31,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66193,7 +66202,7 @@
         <v>221</v>
       </c>
       <c r="AA33">
-        <f>IF(A33=A32,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66275,7 +66284,7 @@
         <v>222</v>
       </c>
       <c r="AA34">
-        <f>IF(A34=A33,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66355,7 +66364,7 @@
         <v>223</v>
       </c>
       <c r="AA35">
-        <f>IF(A35=A34,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66423,7 +66432,7 @@
         <v>224</v>
       </c>
       <c r="AA36">
-        <f>IF(A36=A35,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66503,7 +66512,7 @@
         <v>226</v>
       </c>
       <c r="AA37">
-        <f>IF(A37=A36,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66583,7 +66592,7 @@
         <v>227</v>
       </c>
       <c r="AA38">
-        <f>IF(A38=A37,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66663,7 +66672,7 @@
         <v>228</v>
       </c>
       <c r="AA39">
-        <f>IF(A39=A38,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66728,7 +66737,7 @@
         <v>235</v>
       </c>
       <c r="AA40">
-        <f>IF(A40=A39,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66792,7 +66801,7 @@
         <v>236</v>
       </c>
       <c r="AA41">
-        <f>IF(A41=A40,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66868,7 +66877,7 @@
         <v>244</v>
       </c>
       <c r="AA42">
-        <f>IF(A42=A41,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -66938,7 +66947,7 @@
         <v>255</v>
       </c>
       <c r="AA43">
-        <f>IF(A43=A42,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67008,7 +67017,7 @@
         <v>272</v>
       </c>
       <c r="AA44">
-        <f>IF(A44=A43,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67075,7 +67084,7 @@
         <v>288</v>
       </c>
       <c r="AA45">
-        <f>IF(A45=A44,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67141,7 +67150,7 @@
         <v>318</v>
       </c>
       <c r="AA46">
-        <f>IF(A46=A45,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67207,7 +67216,7 @@
         <v>326</v>
       </c>
       <c r="AA47">
-        <f>IF(A47=A46,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67275,7 +67284,7 @@
         <v>334</v>
       </c>
       <c r="AA48">
-        <f>IF(A48=A47,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67339,7 +67348,7 @@
         <v>336</v>
       </c>
       <c r="AA49">
-        <f>IF(A49=A48,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67405,7 +67414,7 @@
         <v>339</v>
       </c>
       <c r="AA50">
-        <f>IF(A50=A49,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67471,7 +67480,7 @@
         <v>346</v>
       </c>
       <c r="AA51">
-        <f>IF(A51=A50,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67535,7 +67544,7 @@
         <v>355</v>
       </c>
       <c r="AA52">
-        <f>IF(A52=A51,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67601,7 +67610,7 @@
         <v>361</v>
       </c>
       <c r="AA53">
-        <f>IF(A53=A52,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67667,7 +67676,7 @@
         <v>366</v>
       </c>
       <c r="AA54">
-        <f>IF(A54=A53,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67733,7 +67742,7 @@
         <v>367</v>
       </c>
       <c r="AA55">
-        <f>IF(A55=A54,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67799,7 +67808,7 @@
         <v>377</v>
       </c>
       <c r="AA56">
-        <f>IF(A56=A55,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67865,7 +67874,7 @@
         <v>392</v>
       </c>
       <c r="AA57">
-        <f>IF(A57=A56,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67929,7 +67938,7 @@
         <v>393</v>
       </c>
       <c r="AA58">
-        <f>IF(A58=A57,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -67993,7 +68002,7 @@
         <v>402</v>
       </c>
       <c r="AA59">
-        <f>IF(A59=A58,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68057,7 +68066,7 @@
         <v>413</v>
       </c>
       <c r="AA60">
-        <f>IF(A60=A59,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68123,7 +68132,7 @@
         <v>423</v>
       </c>
       <c r="AA61">
-        <f>IF(A61=A60,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68189,7 +68198,7 @@
         <v>424</v>
       </c>
       <c r="AA62">
-        <f>IF(A62=A61,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68255,7 +68264,7 @@
         <v>437</v>
       </c>
       <c r="AA63">
-        <f>IF(A63=A62,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68319,7 +68328,7 @@
         <v>460</v>
       </c>
       <c r="AA64">
-        <f>IF(A64=A63,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68383,7 +68392,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA65">
-        <f>IF(A65=A64,0,1)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
@@ -68447,7 +68456,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA66">
-        <f>IF(A66=A65,0,1)</f>
+        <f t="shared" ref="AA66:AA129" si="1">IF(A66=A65,0,1)</f>
         <v>1</v>
       </c>
     </row>
@@ -68511,7 +68520,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA67">
-        <f>IF(A67=A66,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68575,7 +68584,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA68">
-        <f>IF(A68=A67,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68639,7 +68648,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA69">
-        <f>IF(A69=A68,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68703,7 +68712,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA70">
-        <f>IF(A70=A69,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68767,7 +68776,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA71">
-        <f>IF(A71=A70,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68831,7 +68840,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA72">
-        <f>IF(A72=A71,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68895,7 +68904,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA73">
-        <f>IF(A73=A72,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -68957,7 +68966,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA74">
-        <f>IF(A74=A73,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69021,7 +69030,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA75">
-        <f>IF(A75=A74,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69085,7 +69094,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA76">
-        <f>IF(A76=A75,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69149,7 +69158,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA77">
-        <f>IF(A77=A76,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69213,7 +69222,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA78">
-        <f>IF(A78=A77,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69277,7 +69286,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA79">
-        <f>IF(A79=A78,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69341,7 +69350,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA80">
-        <f>IF(A80=A79,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69405,7 +69414,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA81">
-        <f>IF(A81=A80,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69467,7 +69476,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA82">
-        <f>IF(A82=A81,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69527,7 +69536,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA83">
-        <f>IF(A83=A82,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69590,7 +69599,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA84">
-        <f>IF(A84=A83,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69652,7 +69661,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA85">
-        <f>IF(A85=A84,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69724,7 +69733,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA86">
-        <f>IF(A86=A85,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69794,7 +69803,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA87">
-        <f>IF(A87=A86,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69856,7 +69865,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA88">
-        <f>IF(A88=A87,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69918,7 +69927,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA89">
-        <f>IF(A89=A88,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -69980,7 +69989,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA90">
-        <f>IF(A90=A89,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70042,7 +70051,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA91">
-        <f>IF(A91=A90,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70123,7 +70132,7 @@
         <v>290</v>
       </c>
       <c r="AA92">
-        <f>IF(A92=A91,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70208,7 +70217,7 @@
         <v>77</v>
       </c>
       <c r="AA93">
-        <f>IF(A93=A92,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70293,7 +70302,7 @@
         <v>121</v>
       </c>
       <c r="AA94">
-        <f>IF(A94=A93,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70378,7 +70387,7 @@
         <v>122</v>
       </c>
       <c r="AA95">
-        <f>IF(A95=A94,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70463,7 +70472,7 @@
         <v>124</v>
       </c>
       <c r="AA96">
-        <f>IF(A96=A95,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70548,7 +70557,7 @@
         <v>125</v>
       </c>
       <c r="AA97">
-        <f>IF(A97=A96,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70633,7 +70642,7 @@
         <v>128</v>
       </c>
       <c r="AA98">
-        <f>IF(A98=A97,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70718,7 +70727,7 @@
         <v>172</v>
       </c>
       <c r="AA99">
-        <f>IF(A99=A98,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70803,7 +70812,7 @@
         <v>208</v>
       </c>
       <c r="AA100">
-        <f>IF(A100=A99,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70888,7 +70897,7 @@
         <v>214</v>
       </c>
       <c r="AA101">
-        <f>IF(A101=A100,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -70973,7 +70982,7 @@
         <v>217</v>
       </c>
       <c r="AA102">
-        <f>IF(A102=A101,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71058,7 +71067,7 @@
         <v>218</v>
       </c>
       <c r="AA103">
-        <f>IF(A103=A102,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71141,7 +71150,7 @@
         <v>225</v>
       </c>
       <c r="AA104">
-        <f>IF(A104=A103,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71226,7 +71235,7 @@
         <v>239</v>
       </c>
       <c r="AA105">
-        <f>IF(A105=A104,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71303,7 +71312,7 @@
         <v>241</v>
       </c>
       <c r="AA106">
-        <f>IF(A106=A105,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71386,7 +71395,7 @@
         <v>434</v>
       </c>
       <c r="AA107">
-        <f>IF(A107=A106,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71471,7 +71480,7 @@
         <v>436</v>
       </c>
       <c r="AA108">
-        <f>IF(A108=A107,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71552,7 +71561,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA109">
-        <f>IF(A109=A108,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71635,7 +71644,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA110">
-        <f>IF(A110=A109,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71704,7 +71713,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA111">
-        <f>IF(A111=A110,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71787,7 +71796,7 @@
         <v>68</v>
       </c>
       <c r="AA112">
-        <f>IF(A112=A111,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71872,7 +71881,7 @@
         <v>73</v>
       </c>
       <c r="AA113">
-        <f>IF(A113=A112,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -71957,7 +71966,7 @@
         <v>74</v>
       </c>
       <c r="AA114">
-        <f>IF(A114=A113,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72042,7 +72051,7 @@
         <v>86</v>
       </c>
       <c r="AA115">
-        <f>IF(A115=A114,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72127,7 +72136,7 @@
         <v>95</v>
       </c>
       <c r="AA116">
-        <f>IF(A116=A115,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72212,7 +72221,7 @@
         <v>143</v>
       </c>
       <c r="AA117">
-        <f>IF(A117=A116,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72297,7 +72306,7 @@
         <v>145</v>
       </c>
       <c r="AA118">
-        <f>IF(A118=A117,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72382,7 +72391,7 @@
         <v>146</v>
       </c>
       <c r="AA119">
-        <f>IF(A119=A118,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72467,7 +72476,7 @@
         <v>148</v>
       </c>
       <c r="AA120">
-        <f>IF(A120=A119,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72525,7 +72534,7 @@
         <v>159</v>
       </c>
       <c r="AA121">
-        <f>IF(A121=A120,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72604,7 +72613,7 @@
         <v>167</v>
       </c>
       <c r="AA122">
-        <f>IF(A122=A121,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72677,7 +72686,7 @@
         <v>193</v>
       </c>
       <c r="AA123">
-        <f>IF(A123=A122,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72754,7 +72763,7 @@
         <v>199</v>
       </c>
       <c r="AA124">
-        <f>IF(A124=A123,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72839,7 +72848,7 @@
         <v>203</v>
       </c>
       <c r="AA125">
-        <f>IF(A125=A124,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72912,7 +72921,7 @@
         <v>204</v>
       </c>
       <c r="AA126">
-        <f>IF(A126=A125,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -72985,7 +72994,7 @@
         <v>205</v>
       </c>
       <c r="AA127">
-        <f>IF(A127=A126,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -73058,7 +73067,7 @@
         <v>207</v>
       </c>
       <c r="AA128">
-        <f>IF(A128=A127,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -73143,7 +73152,7 @@
         <v>215</v>
       </c>
       <c r="AA129">
-        <f>IF(A129=A128,0,1)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
@@ -73226,7 +73235,7 @@
         <v>219</v>
       </c>
       <c r="AA130">
-        <f>IF(A130=A129,0,1)</f>
+        <f t="shared" ref="AA130:AA193" si="2">IF(A130=A129,0,1)</f>
         <v>1</v>
       </c>
     </row>
@@ -73309,7 +73318,7 @@
         <v>220</v>
       </c>
       <c r="AA131">
-        <f>IF(A131=A130,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73380,7 +73389,7 @@
         <v>230</v>
       </c>
       <c r="AA132">
-        <f>IF(A132=A131,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73451,7 +73460,7 @@
         <v>231</v>
       </c>
       <c r="AA133">
-        <f>IF(A133=A132,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73522,7 +73531,7 @@
         <v>232</v>
       </c>
       <c r="AA134">
-        <f>IF(A134=A133,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73595,7 +73604,7 @@
         <v>245</v>
       </c>
       <c r="AA135">
-        <f>IF(A135=A134,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73666,7 +73675,7 @@
         <v>246</v>
       </c>
       <c r="AA136">
-        <f>IF(A136=A135,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73739,7 +73748,7 @@
         <v>252</v>
       </c>
       <c r="AA137">
-        <f>IF(A137=A136,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73810,7 +73819,7 @@
         <v>256</v>
       </c>
       <c r="AA138">
-        <f>IF(A138=A137,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73883,7 +73892,7 @@
         <v>260</v>
       </c>
       <c r="AA139">
-        <f>IF(A139=A138,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -73956,7 +73965,7 @@
         <v>261</v>
       </c>
       <c r="AA140">
-        <f>IF(A140=A139,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74027,7 +74036,7 @@
         <v>262</v>
       </c>
       <c r="AA141">
-        <f>IF(A141=A140,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74100,7 +74109,7 @@
         <v>268</v>
       </c>
       <c r="AA142">
-        <f>IF(A142=A141,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74173,7 +74182,7 @@
         <v>269</v>
       </c>
       <c r="AA143">
-        <f>IF(A143=A142,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74246,7 +74255,7 @@
         <v>270</v>
       </c>
       <c r="AA144">
-        <f>IF(A144=A143,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74319,7 +74328,7 @@
         <v>271</v>
       </c>
       <c r="AA145">
-        <f>IF(A145=A144,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74392,7 +74401,7 @@
         <v>273</v>
       </c>
       <c r="AA146">
-        <f>IF(A146=A145,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74477,7 +74486,7 @@
         <v>274</v>
       </c>
       <c r="AA147">
-        <f>IF(A147=A146,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74562,7 +74571,7 @@
         <v>275</v>
       </c>
       <c r="AA148">
-        <f>IF(A148=A147,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74635,7 +74644,7 @@
         <v>276</v>
       </c>
       <c r="AA149">
-        <f>IF(A149=A148,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74708,7 +74717,7 @@
         <v>277</v>
       </c>
       <c r="AA150">
-        <f>IF(A150=A149,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74793,7 +74802,7 @@
         <v>278</v>
       </c>
       <c r="AA151">
-        <f>IF(A151=A150,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74866,7 +74875,7 @@
         <v>282</v>
       </c>
       <c r="AA152">
-        <f>IF(A152=A151,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -74939,7 +74948,7 @@
         <v>283</v>
       </c>
       <c r="AA153">
-        <f>IF(A153=A152,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75012,7 +75021,7 @@
         <v>285</v>
       </c>
       <c r="AA154">
-        <f>IF(A154=A153,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75097,7 +75106,7 @@
         <v>286</v>
       </c>
       <c r="AA155">
-        <f>IF(A155=A154,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75182,7 +75191,7 @@
         <v>292</v>
       </c>
       <c r="AA156">
-        <f>IF(A156=A155,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75267,7 +75276,7 @@
         <v>294</v>
       </c>
       <c r="AA157">
-        <f>IF(A157=A156,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75352,7 +75361,7 @@
         <v>302</v>
       </c>
       <c r="AA158">
-        <f>IF(A158=A157,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75435,7 +75444,7 @@
         <v>303</v>
       </c>
       <c r="AA159">
-        <f>IF(A159=A158,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75508,7 +75517,7 @@
         <v>304</v>
       </c>
       <c r="AA160">
-        <f>IF(A160=A159,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75581,7 +75590,7 @@
         <v>323</v>
       </c>
       <c r="AA161">
-        <f>IF(A161=A160,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75654,7 +75663,7 @@
         <v>324</v>
       </c>
       <c r="AA162">
-        <f>IF(A162=A161,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75727,7 +75736,7 @@
         <v>325</v>
       </c>
       <c r="AA163">
-        <f>IF(A163=A162,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75800,7 +75809,7 @@
         <v>327</v>
       </c>
       <c r="AA164">
-        <f>IF(A164=A163,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75873,7 +75882,7 @@
         <v>332</v>
       </c>
       <c r="AA165">
-        <f>IF(A165=A164,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -75946,7 +75955,7 @@
         <v>337</v>
       </c>
       <c r="AA166">
-        <f>IF(A166=A165,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76019,7 +76028,7 @@
         <v>338</v>
       </c>
       <c r="AA167">
-        <f>IF(A167=A166,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76092,7 +76101,7 @@
         <v>341</v>
       </c>
       <c r="AA168">
-        <f>IF(A168=A167,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76165,7 +76174,7 @@
         <v>344</v>
       </c>
       <c r="AA169">
-        <f>IF(A169=A168,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76238,7 +76247,7 @@
         <v>356</v>
       </c>
       <c r="AA170">
-        <f>IF(A170=A169,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76307,7 +76316,7 @@
         <v>357</v>
       </c>
       <c r="AA171">
-        <f>IF(A171=A170,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76380,7 +76389,7 @@
         <v>358</v>
       </c>
       <c r="AA172">
-        <f>IF(A172=A171,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76449,7 +76458,7 @@
         <v>359</v>
       </c>
       <c r="AA173">
-        <f>IF(A173=A172,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76534,7 +76543,7 @@
         <v>362</v>
       </c>
       <c r="AA174">
-        <f>IF(A174=A173,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76605,7 +76614,7 @@
         <v>363</v>
       </c>
       <c r="AA175">
-        <f>IF(A175=A174,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76678,7 +76687,7 @@
         <v>364</v>
       </c>
       <c r="AA176">
-        <f>IF(A176=A175,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76763,7 +76772,7 @@
         <v>369</v>
       </c>
       <c r="AA177">
-        <f>IF(A177=A176,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76836,7 +76845,7 @@
         <v>371</v>
       </c>
       <c r="AA178">
-        <f>IF(A178=A177,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76921,7 +76930,7 @@
         <v>375</v>
       </c>
       <c r="AA179">
-        <f>IF(A179=A178,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -76994,7 +77003,7 @@
         <v>376</v>
       </c>
       <c r="AA180">
-        <f>IF(A180=A179,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77067,7 +77076,7 @@
         <v>379</v>
       </c>
       <c r="AA181">
-        <f>IF(A181=A180,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77140,7 +77149,7 @@
         <v>381</v>
       </c>
       <c r="AA182">
-        <f>IF(A182=A181,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77213,7 +77222,7 @@
         <v>382</v>
       </c>
       <c r="AA183">
-        <f>IF(A183=A182,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77286,7 +77295,7 @@
         <v>383</v>
       </c>
       <c r="AA184">
-        <f>IF(A184=A183,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77359,7 +77368,7 @@
         <v>384</v>
       </c>
       <c r="AA185">
-        <f>IF(A185=A184,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77432,7 +77441,7 @@
         <v>385</v>
       </c>
       <c r="AA186">
-        <f>IF(A186=A185,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77517,7 +77526,7 @@
         <v>386</v>
       </c>
       <c r="AA187">
-        <f>IF(A187=A186,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77598,7 +77607,7 @@
         <v>389</v>
       </c>
       <c r="AA188">
-        <f>IF(A188=A187,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77671,7 +77680,7 @@
         <v>397</v>
       </c>
       <c r="AA189">
-        <f>IF(A189=A188,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77744,7 +77753,7 @@
         <v>398</v>
       </c>
       <c r="AA190">
-        <f>IF(A190=A189,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77817,7 +77826,7 @@
         <v>399</v>
       </c>
       <c r="AA191">
-        <f>IF(A191=A190,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77890,7 +77899,7 @@
         <v>400</v>
       </c>
       <c r="AA192">
-        <f>IF(A192=A191,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -77963,7 +77972,7 @@
         <v>401</v>
       </c>
       <c r="AA193">
-        <f>IF(A193=A192,0,1)</f>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
@@ -78036,7 +78045,7 @@
         <v>403</v>
       </c>
       <c r="AA194">
-        <f>IF(A194=A193,0,1)</f>
+        <f t="shared" ref="AA194:AA257" si="3">IF(A194=A193,0,1)</f>
         <v>1</v>
       </c>
     </row>
@@ -78121,7 +78130,7 @@
         <v>408</v>
       </c>
       <c r="AA195">
-        <f>IF(A195=A194,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78194,7 +78203,7 @@
         <v>422</v>
       </c>
       <c r="AA196">
-        <f>IF(A196=A195,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78261,7 +78270,7 @@
         <v>426</v>
       </c>
       <c r="AA197">
-        <f>IF(A197=A196,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78346,7 +78355,7 @@
         <v>427</v>
       </c>
       <c r="AA198">
-        <f>IF(A198=A197,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78431,7 +78440,7 @@
         <v>428</v>
       </c>
       <c r="AA199">
-        <f>IF(A199=A198,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78516,7 +78525,7 @@
         <v>429</v>
       </c>
       <c r="AA200">
-        <f>IF(A200=A199,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78601,7 +78610,7 @@
         <v>430</v>
       </c>
       <c r="AA201">
-        <f>IF(A201=A200,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78686,7 +78695,7 @@
         <v>433</v>
       </c>
       <c r="AA202">
-        <f>IF(A202=A201,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78769,7 +78778,7 @@
         <v>435</v>
       </c>
       <c r="AA203">
-        <f>IF(A203=A202,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78854,7 +78863,7 @@
         <v>439</v>
       </c>
       <c r="AA204">
-        <f>IF(A204=A203,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -78939,7 +78948,7 @@
         <v>440</v>
       </c>
       <c r="AA205">
-        <f>IF(A205=A204,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79006,7 +79015,7 @@
         <v>444</v>
       </c>
       <c r="AA206">
-        <f>IF(A206=A205,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79075,7 +79084,7 @@
         <v>445</v>
       </c>
       <c r="AA207">
-        <f>IF(A207=A206,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79144,7 +79153,7 @@
         <v>447</v>
       </c>
       <c r="AA208">
-        <f>IF(A208=A207,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79213,7 +79222,7 @@
         <v>448</v>
       </c>
       <c r="AA209">
-        <f>IF(A209=A208,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79282,7 +79291,7 @@
         <v>451</v>
       </c>
       <c r="AA210">
-        <f>IF(A210=A209,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79347,7 +79356,7 @@
         <v>452</v>
       </c>
       <c r="AA211">
-        <f>IF(A211=A210,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79416,7 +79425,7 @@
         <v>466</v>
       </c>
       <c r="AA212">
-        <f>IF(A212=A211,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79485,7 +79494,7 @@
         <v>467</v>
       </c>
       <c r="AA213">
-        <f>IF(A213=A212,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79554,7 +79563,7 @@
         <v>468</v>
       </c>
       <c r="AA214">
-        <f>IF(A214=A213,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79639,7 +79648,7 @@
         <v>473</v>
       </c>
       <c r="AA215">
-        <f>IF(A215=A214,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79720,7 +79729,7 @@
         <v>474</v>
       </c>
       <c r="AA216">
-        <f>IF(A216=A215,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79789,7 +79798,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA217">
-        <f>IF(A217=A216,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79874,7 +79883,7 @@
         <v>476</v>
       </c>
       <c r="AA218">
-        <f>IF(A218=A217,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -79953,7 +79962,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA219">
-        <f>IF(A219=A218,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80034,7 +80043,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA220">
-        <f>IF(A220=A219,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80115,7 +80124,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA221">
-        <f>IF(A221=A220,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80196,7 +80205,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA222">
-        <f>IF(A222=A221,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80265,7 +80274,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA223">
-        <f>IF(A223=A222,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80332,7 +80341,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA224">
-        <f>IF(A224=A223,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80399,7 +80408,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA225">
-        <f>IF(A225=A224,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80466,7 +80475,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA226">
-        <f>IF(A226=A225,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80531,7 +80540,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA227">
-        <f>IF(A227=A226,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80594,7 +80603,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA228">
-        <f>IF(A228=A227,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80657,7 +80666,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA229">
-        <f>IF(A229=A228,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80742,7 +80751,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA230">
-        <f>IF(A230=A229,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80827,7 +80836,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA231">
-        <f>IF(A231=A230,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80912,7 +80921,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA232">
-        <f>IF(A232=A231,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -80975,7 +80984,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA233">
-        <f>IF(A233=A232,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81038,7 +81047,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA234">
-        <f>IF(A234=A233,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81115,7 +81124,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA235">
-        <f>IF(A235=A234,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81200,7 +81209,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA236">
-        <f>IF(A236=A235,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81285,7 +81294,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA237">
-        <f>IF(A237=A236,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81370,7 +81379,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA238">
-        <f>IF(A238=A237,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81455,7 +81464,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA239">
-        <f>IF(A239=A238,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81520,7 +81529,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA240">
-        <f>IF(A240=A239,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81583,7 +81592,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA241">
-        <f>IF(A241=A240,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81646,7 +81655,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA242">
-        <f>IF(A242=A241,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81711,7 +81720,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA243">
-        <f>IF(A243=A242,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81794,7 +81803,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA244">
-        <f>IF(A244=A243,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81877,7 +81886,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA245">
-        <f>IF(A245=A244,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -81942,7 +81951,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA246">
-        <f>IF(A246=A245,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82007,7 +82016,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA247">
-        <f>IF(A247=A246,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82070,7 +82079,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA248">
-        <f>IF(A248=A247,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82133,7 +82142,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA249">
-        <f>IF(A249=A248,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82218,7 +82227,7 @@
         <v>69</v>
       </c>
       <c r="AA250">
-        <f>IF(A250=A249,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82303,7 +82312,7 @@
         <v>111</v>
       </c>
       <c r="AA251">
-        <f>IF(A251=A250,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82388,7 +82397,7 @@
         <v>197</v>
       </c>
       <c r="AA252">
-        <f>IF(A252=A251,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82473,7 +82482,7 @@
         <v>213</v>
       </c>
       <c r="AA253">
-        <f>IF(A253=A252,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82556,7 +82565,7 @@
         <v>233</v>
       </c>
       <c r="AA254">
-        <f>IF(A254=A253,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82639,7 +82648,7 @@
         <v>234</v>
       </c>
       <c r="AA255">
-        <f>IF(A255=A254,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82720,7 +82729,7 @@
         <v>238</v>
       </c>
       <c r="AA256">
-        <f>IF(A256=A255,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82803,7 +82812,7 @@
         <v>240</v>
       </c>
       <c r="AA257">
-        <f>IF(A257=A256,0,1)</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
@@ -82886,7 +82895,7 @@
         <v>251</v>
       </c>
       <c r="AA258">
-        <f>IF(A258=A257,0,1)</f>
+        <f t="shared" ref="AA258:AA298" si="4">IF(A258=A257,0,1)</f>
         <v>1</v>
       </c>
     </row>
@@ -82950,7 +82959,7 @@
         <v>254</v>
       </c>
       <c r="AA259">
-        <f>IF(A259=A258,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83035,7 +83044,7 @@
         <v>263</v>
       </c>
       <c r="AA260">
-        <f>IF(A260=A259,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83120,7 +83129,7 @@
         <v>265</v>
       </c>
       <c r="AA261">
-        <f>IF(A261=A260,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83205,7 +83214,7 @@
         <v>266</v>
       </c>
       <c r="AA262">
-        <f>IF(A262=A261,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83290,7 +83299,7 @@
         <v>300</v>
       </c>
       <c r="AA263">
-        <f>IF(A263=A262,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83375,7 +83384,7 @@
         <v>301</v>
       </c>
       <c r="AA264">
-        <f>IF(A264=A263,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83458,7 +83467,7 @@
         <v>306</v>
       </c>
       <c r="AA265">
-        <f>IF(A265=A264,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83543,7 +83552,7 @@
         <v>347</v>
       </c>
       <c r="AA266">
-        <f>IF(A266=A265,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83628,7 +83637,7 @@
         <v>348</v>
       </c>
       <c r="AA267">
-        <f>IF(A267=A266,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83711,7 +83720,7 @@
         <v>351</v>
       </c>
       <c r="AA268">
-        <f>IF(A268=A267,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83794,7 +83803,7 @@
         <v>352</v>
       </c>
       <c r="AA269">
-        <f>IF(A269=A268,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83875,7 +83884,7 @@
         <v>368</v>
       </c>
       <c r="AA270">
-        <f>IF(A270=A269,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -83956,7 +83965,7 @@
         <v>372</v>
       </c>
       <c r="AA271">
-        <f>IF(A271=A270,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84041,7 +84050,7 @@
         <v>373</v>
       </c>
       <c r="AA272">
-        <f>IF(A272=A271,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84126,7 +84135,7 @@
         <v>390</v>
       </c>
       <c r="AA273">
-        <f>IF(A273=A272,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84211,7 +84220,7 @@
         <v>394</v>
       </c>
       <c r="AA274">
-        <f>IF(A274=A273,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84294,7 +84303,7 @@
         <v>395</v>
       </c>
       <c r="AA275">
-        <f>IF(A275=A274,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84373,7 +84382,7 @@
         <v>409</v>
       </c>
       <c r="AA276">
-        <f>IF(A276=A275,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84458,7 +84467,7 @@
         <v>414</v>
       </c>
       <c r="AA277">
-        <f>IF(A277=A276,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84543,7 +84552,7 @@
         <v>415</v>
       </c>
       <c r="AA278">
-        <f>IF(A278=A277,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84628,7 +84637,7 @@
         <v>416</v>
       </c>
       <c r="AA279">
-        <f>IF(A279=A278,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84713,7 +84722,7 @@
         <v>417</v>
       </c>
       <c r="AA280">
-        <f>IF(A280=A279,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84798,7 +84807,7 @@
         <v>418</v>
       </c>
       <c r="AA281">
-        <f>IF(A281=A280,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84883,7 +84892,7 @@
         <v>420</v>
       </c>
       <c r="AA282">
-        <f>IF(A282=A281,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -84964,7 +84973,7 @@
         <v>431</v>
       </c>
       <c r="AA283">
-        <f>IF(A283=A282,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85049,7 +85058,7 @@
         <v>432</v>
       </c>
       <c r="AA284">
-        <f>IF(A284=A283,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85126,7 +85135,7 @@
         <v>453</v>
       </c>
       <c r="AA285">
-        <f>IF(A285=A284,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85199,7 +85208,7 @@
         <v>455</v>
       </c>
       <c r="AA286">
-        <f>IF(A286=A285,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85278,7 +85287,7 @@
         <v>456</v>
       </c>
       <c r="AA287">
-        <f>IF(A287=A286,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85357,7 +85366,7 @@
         <v>457</v>
       </c>
       <c r="AA288">
-        <f>IF(A288=A287,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85440,7 +85449,7 @@
         <v>469</v>
       </c>
       <c r="AA289">
-        <f>IF(A289=A288,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85525,7 +85534,7 @@
         <v>470</v>
       </c>
       <c r="AA290">
-        <f>IF(A290=A289,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85610,7 +85619,7 @@
         <v>471</v>
       </c>
       <c r="AA291">
-        <f>IF(A291=A290,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85685,7 +85694,7 @@
         <v>484</v>
       </c>
       <c r="AA292">
-        <f>IF(A292=A291,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85768,7 +85777,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA293">
-        <f>IF(A293=A292,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85851,7 +85860,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA294">
-        <f>IF(A294=A293,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85920,7 +85929,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA295">
-        <f>IF(A295=A294,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -85982,7 +85991,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA296">
-        <f>IF(A296=A295,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -86047,7 +86056,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA297">
-        <f>IF(A297=A296,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
@@ -86130,7 +86139,7 @@
         <v>#N/A</v>
       </c>
       <c r="AA298">
-        <f>IF(A298=A297,0,1)</f>
+        <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>

--- a/data/raw/lmi_reporte.xlsx
+++ b/data/raw/lmi_reporte.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5f15395a9ed9a48f/Proyectos_DS/Indicadores_Oportunidad_Mejora/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08A65329-72D2-429A-A131-7D2081412124}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{2553D8ED-1A7D-4653-A81C-B563898AD95F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AB4F2B7-D6D9-4EFC-A9D7-9F152B215129}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{0ABA65E9-32CA-4FC8-8179-9B0EBD2C31C1}"/>
   </bookViews>
@@ -6620,7 +6620,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:Y786"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6705,7 +6704,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>84</v>
       </c>
@@ -6775,7 +6774,7 @@
       <c r="W2" s="3"/>
       <c r="X2" s="3"/>
     </row>
-    <row r="3" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>85</v>
       </c>
@@ -6845,7 +6844,7 @@
       <c r="W3" s="3"/>
       <c r="X3" s="3"/>
     </row>
-    <row r="4" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>87</v>
       </c>
@@ -6915,7 +6914,7 @@
       <c r="W4" s="3"/>
       <c r="X4" s="3"/>
     </row>
-    <row r="5" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>88</v>
       </c>
@@ -6985,7 +6984,7 @@
       <c r="W5" s="3"/>
       <c r="X5" s="3"/>
     </row>
-    <row r="6" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>89</v>
       </c>
@@ -7055,7 +7054,7 @@
       <c r="W6" s="3"/>
       <c r="X6" s="3"/>
     </row>
-    <row r="7" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>90</v>
       </c>
@@ -7125,7 +7124,7 @@
       <c r="W7" s="3"/>
       <c r="X7" s="3"/>
     </row>
-    <row r="8" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>91</v>
       </c>
@@ -7195,7 +7194,7 @@
       <c r="W8" s="3"/>
       <c r="X8" s="3"/>
     </row>
-    <row r="9" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>92</v>
       </c>
@@ -7265,7 +7264,7 @@
       <c r="W9" s="3"/>
       <c r="X9" s="3"/>
     </row>
-    <row r="10" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>94</v>
       </c>
@@ -7335,7 +7334,7 @@
       <c r="W10" s="3"/>
       <c r="X10" s="3"/>
     </row>
-    <row r="11" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>100</v>
       </c>
@@ -7405,7 +7404,7 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>104</v>
       </c>
@@ -7475,7 +7474,7 @@
       <c r="W12" s="3"/>
       <c r="X12" s="3"/>
     </row>
-    <row r="13" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>106</v>
       </c>
@@ -7545,7 +7544,7 @@
       <c r="W13" s="3"/>
       <c r="X13" s="3"/>
     </row>
-    <row r="14" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>109</v>
       </c>
@@ -7612,7 +7611,7 @@
       <c r="X14" s="3"/>
       <c r="Y14" s="3"/>
     </row>
-    <row r="15" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>112</v>
       </c>
@@ -7681,7 +7680,7 @@
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
     </row>
-    <row r="16" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>113</v>
       </c>
@@ -7750,7 +7749,7 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
     </row>
-    <row r="17" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>114</v>
       </c>
@@ -7819,7 +7818,7 @@
       <c r="X17" s="3"/>
       <c r="Y17" s="3"/>
     </row>
-    <row r="18" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>115</v>
       </c>
@@ -7888,7 +7887,7 @@
       <c r="X18" s="3"/>
       <c r="Y18" s="3"/>
     </row>
-    <row r="19" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>116</v>
       </c>
@@ -7949,7 +7948,7 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
     </row>
-    <row r="20" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>117</v>
       </c>
@@ -8018,7 +8017,7 @@
       <c r="X20" s="3"/>
       <c r="Y20" s="3"/>
     </row>
-    <row r="21" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>118</v>
       </c>
@@ -8087,7 +8086,7 @@
       <c r="X21" s="3"/>
       <c r="Y21" s="3"/>
     </row>
-    <row r="22" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>126</v>
       </c>
@@ -8157,7 +8156,7 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
-    <row r="23" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>127</v>
       </c>
@@ -8227,7 +8226,7 @@
       <c r="W23" s="3"/>
       <c r="X23" s="3"/>
     </row>
-    <row r="24" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>133</v>
       </c>
@@ -8294,7 +8293,7 @@
       <c r="X24" s="3"/>
       <c r="Y24" s="3"/>
     </row>
-    <row r="25" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>144</v>
       </c>
@@ -8358,7 +8357,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>147</v>
       </c>
@@ -8418,7 +8417,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>150</v>
       </c>
@@ -8481,7 +8480,7 @@
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
     </row>
-    <row r="28" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>151</v>
       </c>
@@ -8546,7 +8545,7 @@
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
     </row>
-    <row r="29" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>200</v>
       </c>
@@ -8608,7 +8607,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>202</v>
       </c>
@@ -8666,7 +8665,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>206</v>
       </c>
@@ -8724,7 +8723,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>216</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>216</v>
       </c>
@@ -8872,7 +8871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>216</v>
       </c>
@@ -8946,7 +8945,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="35" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>216</v>
       </c>
@@ -9020,7 +9019,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="36" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>216</v>
       </c>
@@ -9094,7 +9093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="37" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>216</v>
       </c>
@@ -9168,7 +9167,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>216</v>
       </c>
@@ -9242,7 +9241,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="39" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>221</v>
       </c>
@@ -9306,7 +9305,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
     </row>
-    <row r="40" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>221</v>
       </c>
@@ -9380,7 +9379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>221</v>
       </c>
@@ -9454,7 +9453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="42" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>221</v>
       </c>
@@ -9528,7 +9527,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="43" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>221</v>
       </c>
@@ -9602,7 +9601,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="44" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>221</v>
       </c>
@@ -9676,7 +9675,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="45" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>221</v>
       </c>
@@ -9750,7 +9749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>222</v>
       </c>
@@ -9824,7 +9823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>222</v>
       </c>
@@ -9898,7 +9897,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="48" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>223</v>
       </c>
@@ -9970,7 +9969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>223</v>
       </c>
@@ -10044,7 +10043,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="50" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>223</v>
       </c>
@@ -10118,7 +10117,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="51" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>224</v>
       </c>
@@ -10178,7 +10177,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>224</v>
       </c>
@@ -10252,7 +10251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="53" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>224</v>
       </c>
@@ -10326,7 +10325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="54" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>224</v>
       </c>
@@ -10400,7 +10399,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="55" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>224</v>
       </c>
@@ -10472,7 +10471,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="56" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>224</v>
       </c>
@@ -10546,7 +10545,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>224</v>
       </c>
@@ -10620,7 +10619,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="58" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>226</v>
       </c>
@@ -10692,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>226</v>
       </c>
@@ -10766,7 +10765,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="60" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>226</v>
       </c>
@@ -10840,7 +10839,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="61" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>226</v>
       </c>
@@ -10914,7 +10913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>226</v>
       </c>
@@ -10988,7 +10987,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="63" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>226</v>
       </c>
@@ -11062,7 +11061,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="64" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>226</v>
       </c>
@@ -11136,7 +11135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>227</v>
       </c>
@@ -11208,7 +11207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>227</v>
       </c>
@@ -11282,7 +11281,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>227</v>
       </c>
@@ -11352,7 +11351,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="68" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>227</v>
       </c>
@@ -11426,7 +11425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="69" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>227</v>
       </c>
@@ -11496,7 +11495,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="70" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>227</v>
       </c>
@@ -11566,7 +11565,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="71" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>227</v>
       </c>
@@ -11640,7 +11639,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>228</v>
       </c>
@@ -11712,7 +11711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>228</v>
       </c>
@@ -11786,7 +11785,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="74" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>228</v>
       </c>
@@ -11860,7 +11859,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="75" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>228</v>
       </c>
@@ -11934,7 +11933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="76" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>228</v>
       </c>
@@ -12008,7 +12007,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="77" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>228</v>
       </c>
@@ -12082,7 +12081,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>228</v>
       </c>
@@ -12156,7 +12155,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="79" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>235</v>
       </c>
@@ -12213,7 +12212,7 @@
       <c r="X79" s="3"/>
       <c r="Y79" s="3"/>
     </row>
-    <row r="80" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>236</v>
       </c>
@@ -12269,7 +12268,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>244</v>
       </c>
@@ -12337,7 +12336,7 @@
       <c r="W81" s="3"/>
       <c r="X81" s="3"/>
     </row>
-    <row r="82" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>255</v>
       </c>
@@ -12399,7 +12398,7 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
     </row>
-    <row r="83" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>255</v>
       </c>
@@ -12473,7 +12472,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>255</v>
       </c>
@@ -12547,7 +12546,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="85" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>255</v>
       </c>
@@ -12621,7 +12620,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="86" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>255</v>
       </c>
@@ -12695,7 +12694,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="87" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>255</v>
       </c>
@@ -12769,7 +12768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>255</v>
       </c>
@@ -12843,7 +12842,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="89" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>272</v>
       </c>
@@ -12905,7 +12904,7 @@
       <c r="W89" s="3"/>
       <c r="X89" s="3"/>
     </row>
-    <row r="90" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>288</v>
       </c>
@@ -12964,7 +12963,7 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
     </row>
-    <row r="91" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>318</v>
       </c>
@@ -13022,7 +13021,7 @@
       <c r="W91" s="3"/>
       <c r="X91" s="3"/>
     </row>
-    <row r="92" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>326</v>
       </c>
@@ -13080,7 +13079,7 @@
       <c r="W92" s="3"/>
       <c r="X92" s="3"/>
     </row>
-    <row r="93" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>334</v>
       </c>
@@ -13140,7 +13139,7 @@
       <c r="W93" s="3"/>
       <c r="X93" s="3"/>
     </row>
-    <row r="94" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>336</v>
       </c>
@@ -13196,7 +13195,7 @@
       <c r="W94" s="3"/>
       <c r="X94" s="3"/>
     </row>
-    <row r="95" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>339</v>
       </c>
@@ -13254,7 +13253,7 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
     </row>
-    <row r="96" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>346</v>
       </c>
@@ -13312,7 +13311,7 @@
       <c r="W96" s="3"/>
       <c r="X96" s="3"/>
     </row>
-    <row r="97" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>355</v>
       </c>
@@ -13368,7 +13367,7 @@
       <c r="W97" s="3"/>
       <c r="X97" s="3"/>
     </row>
-    <row r="98" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>361</v>
       </c>
@@ -13426,7 +13425,7 @@
       <c r="W98" s="3"/>
       <c r="X98" s="3"/>
     </row>
-    <row r="99" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>366</v>
       </c>
@@ -13484,7 +13483,7 @@
       <c r="W99" s="3"/>
       <c r="X99" s="3"/>
     </row>
-    <row r="100" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>367</v>
       </c>
@@ -13542,7 +13541,7 @@
       <c r="W100" s="3"/>
       <c r="X100" s="3"/>
     </row>
-    <row r="101" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>377</v>
       </c>
@@ -13600,7 +13599,7 @@
       <c r="W101" s="3"/>
       <c r="X101" s="3"/>
     </row>
-    <row r="102" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>392</v>
       </c>
@@ -13658,7 +13657,7 @@
       <c r="W102" s="3"/>
       <c r="X102" s="3"/>
     </row>
-    <row r="103" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>393</v>
       </c>
@@ -13714,7 +13713,7 @@
       <c r="W103" s="3"/>
       <c r="X103" s="3"/>
     </row>
-    <row r="104" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>402</v>
       </c>
@@ -13770,7 +13769,7 @@
       <c r="W104" s="3"/>
       <c r="X104" s="3"/>
     </row>
-    <row r="105" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>413</v>
       </c>
@@ -13826,7 +13825,7 @@
       <c r="W105" s="3"/>
       <c r="X105" s="3"/>
     </row>
-    <row r="106" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>423</v>
       </c>
@@ -13884,7 +13883,7 @@
       <c r="W106" s="3"/>
       <c r="X106" s="3"/>
     </row>
-    <row r="107" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>424</v>
       </c>
@@ -13942,7 +13941,7 @@
       <c r="W107" s="3"/>
       <c r="X107" s="3"/>
     </row>
-    <row r="108" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>437</v>
       </c>
@@ -14000,7 +13999,7 @@
       <c r="W108" s="3"/>
       <c r="X108" s="3"/>
     </row>
-    <row r="109" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>460</v>
       </c>
@@ -14056,7 +14055,7 @@
       <c r="W109" s="3"/>
       <c r="X109" s="3"/>
     </row>
-    <row r="110" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>487</v>
       </c>
@@ -14112,7 +14111,7 @@
       <c r="W110" s="3"/>
       <c r="X110" s="3"/>
     </row>
-    <row r="111" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>490</v>
       </c>
@@ -14168,7 +14167,7 @@
       <c r="W111" s="3"/>
       <c r="X111" s="3"/>
     </row>
-    <row r="112" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>491</v>
       </c>
@@ -14224,7 +14223,7 @@
       <c r="W112" s="3"/>
       <c r="X112" s="3"/>
     </row>
-    <row r="113" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>492</v>
       </c>
@@ -14280,7 +14279,7 @@
       <c r="W113" s="3"/>
       <c r="X113" s="3"/>
     </row>
-    <row r="114" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>493</v>
       </c>
@@ -14336,7 +14335,7 @@
       <c r="W114" s="3"/>
       <c r="X114" s="3"/>
     </row>
-    <row r="115" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>494</v>
       </c>
@@ -14448,7 +14447,7 @@
       <c r="W116" s="3"/>
       <c r="X116" s="3"/>
     </row>
-    <row r="117" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>496</v>
       </c>
@@ -14504,7 +14503,7 @@
       <c r="W117" s="3"/>
       <c r="X117" s="3"/>
     </row>
-    <row r="118" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>498</v>
       </c>
@@ -14560,7 +14559,7 @@
       <c r="W118" s="3"/>
       <c r="X118" s="3"/>
     </row>
-    <row r="119" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>499</v>
       </c>
@@ -14614,7 +14613,7 @@
       <c r="W119" s="3"/>
       <c r="X119" s="3"/>
     </row>
-    <row r="120" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>500</v>
       </c>
@@ -14670,7 +14669,7 @@
       <c r="W120" s="3"/>
       <c r="X120" s="3"/>
     </row>
-    <row r="121" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>501</v>
       </c>
@@ -14726,7 +14725,7 @@
       <c r="W121" s="3"/>
       <c r="X121" s="3"/>
     </row>
-    <row r="122" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>502</v>
       </c>
@@ -14782,7 +14781,7 @@
       <c r="W122" s="3"/>
       <c r="X122" s="3"/>
     </row>
-    <row r="123" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>503</v>
       </c>
@@ -14838,7 +14837,7 @@
       <c r="W123" s="3"/>
       <c r="X123" s="3"/>
     </row>
-    <row r="124" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>504</v>
       </c>
@@ -14894,7 +14893,7 @@
       <c r="W124" s="3"/>
       <c r="X124" s="3"/>
     </row>
-    <row r="125" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>505</v>
       </c>
@@ -14950,7 +14949,7 @@
       <c r="W125" s="3"/>
       <c r="X125" s="3"/>
     </row>
-    <row r="126" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>508</v>
       </c>
@@ -15006,7 +15005,7 @@
       <c r="W126" s="3"/>
       <c r="X126" s="3"/>
     </row>
-    <row r="127" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>522</v>
       </c>
@@ -15060,7 +15059,7 @@
       <c r="W127" s="3"/>
       <c r="X127" s="3"/>
     </row>
-    <row r="128" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>527</v>
       </c>
@@ -15112,7 +15111,7 @@
       <c r="W128" s="3"/>
       <c r="X128" s="3"/>
     </row>
-    <row r="129" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>528</v>
       </c>
@@ -15167,7 +15166,7 @@
       <c r="X129" s="3"/>
       <c r="Y129" s="3"/>
     </row>
-    <row r="130" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>541</v>
       </c>
@@ -15221,7 +15220,7 @@
       <c r="W130" s="3"/>
       <c r="X130" s="3"/>
     </row>
-    <row r="131" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>542</v>
       </c>
@@ -15285,7 +15284,7 @@
       <c r="W131" s="3"/>
       <c r="X131" s="3"/>
     </row>
-    <row r="132" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>542</v>
       </c>
@@ -15359,7 +15358,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="133" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>542</v>
       </c>
@@ -15433,7 +15432,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="134" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>542</v>
       </c>
@@ -15507,7 +15506,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="135" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>542</v>
       </c>
@@ -15581,7 +15580,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="136" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>546</v>
       </c>
@@ -15643,7 +15642,7 @@
       <c r="W136" s="3"/>
       <c r="X136" s="3"/>
     </row>
-    <row r="137" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>546</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="138" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>546</v>
       </c>
@@ -15785,7 +15784,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="139" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>546</v>
       </c>
@@ -15856,7 +15855,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="140" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>547</v>
       </c>
@@ -15910,7 +15909,7 @@
       <c r="W140" s="3"/>
       <c r="X140" s="3"/>
     </row>
-    <row r="141" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>552</v>
       </c>
@@ -15964,7 +15963,7 @@
       <c r="W141" s="3"/>
       <c r="X141" s="3"/>
     </row>
-    <row r="142" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>553</v>
       </c>
@@ -16018,7 +16017,7 @@
       <c r="W142" s="3"/>
       <c r="X142" s="3"/>
     </row>
-    <row r="143" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>556</v>
       </c>
@@ -16072,7 +16071,7 @@
       <c r="W143" s="3"/>
       <c r="X143" s="3"/>
     </row>
-    <row r="144" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>290</v>
       </c>
@@ -16145,7 +16144,7 @@
         <v>91.666666666666657</v>
       </c>
     </row>
-    <row r="145" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>290</v>
       </c>
@@ -16219,7 +16218,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="146" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>290</v>
       </c>
@@ -16293,7 +16292,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="147" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>290</v>
       </c>
@@ -16367,7 +16366,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="148" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>290</v>
       </c>
@@ -16441,7 +16440,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>290</v>
       </c>
@@ -16515,7 +16514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="150" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>290</v>
       </c>
@@ -16589,7 +16588,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="151" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>290</v>
       </c>
@@ -16663,7 +16662,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="152" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>290</v>
       </c>
@@ -16737,7 +16736,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="153" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>290</v>
       </c>
@@ -16811,7 +16810,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="154" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>77</v>
       </c>
@@ -16888,7 +16887,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>121</v>
       </c>
@@ -16965,7 +16964,7 @@
         <v>99.18</v>
       </c>
     </row>
-    <row r="156" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>122</v>
       </c>
@@ -17042,7 +17041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>124</v>
       </c>
@@ -17119,7 +17118,7 @@
         <v>9.1157702825888781E-2</v>
       </c>
     </row>
-    <row r="158" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>125</v>
       </c>
@@ -17196,7 +17195,7 @@
         <v>0.27347310847766643</v>
       </c>
     </row>
-    <row r="159" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>128</v>
       </c>
@@ -17273,7 +17272,7 @@
         <v>0.86</v>
       </c>
     </row>
-    <row r="160" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>172</v>
       </c>
@@ -17350,7 +17349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>208</v>
       </c>
@@ -17427,7 +17426,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="162" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>208</v>
       </c>
@@ -17504,7 +17503,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="163" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>208</v>
       </c>
@@ -17581,7 +17580,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="164" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>208</v>
       </c>
@@ -17658,7 +17657,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="165" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>208</v>
       </c>
@@ -17735,7 +17734,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="166" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>208</v>
       </c>
@@ -17812,7 +17811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>208</v>
       </c>
@@ -17889,7 +17888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>214</v>
       </c>
@@ -17966,7 +17965,7 @@
         <v>2054.7600000000002</v>
       </c>
     </row>
-    <row r="169" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>214</v>
       </c>
@@ -18043,7 +18042,7 @@
         <v>1130.94</v>
       </c>
     </row>
-    <row r="170" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>214</v>
       </c>
@@ -18120,7 +18119,7 @@
         <v>406.56</v>
       </c>
     </row>
-    <row r="171" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>214</v>
       </c>
@@ -18197,7 +18196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="172" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>214</v>
       </c>
@@ -18274,7 +18273,7 @@
         <v>406.9</v>
       </c>
     </row>
-    <row r="173" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>214</v>
       </c>
@@ -18351,7 +18350,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="174" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>214</v>
       </c>
@@ -18428,7 +18427,7 @@
         <v>110.36</v>
       </c>
     </row>
-    <row r="175" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>217</v>
       </c>
@@ -18505,7 +18504,7 @@
         <v>139.19</v>
       </c>
     </row>
-    <row r="176" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>217</v>
       </c>
@@ -18582,7 +18581,7 @@
         <v>240.68</v>
       </c>
     </row>
-    <row r="177" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>217</v>
       </c>
@@ -18659,7 +18658,7 @@
         <v>19.850000000000001</v>
       </c>
     </row>
-    <row r="178" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>217</v>
       </c>
@@ -18736,7 +18735,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="179" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>217</v>
       </c>
@@ -18813,7 +18812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>217</v>
       </c>
@@ -18890,7 +18889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="181" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>217</v>
       </c>
@@ -18967,7 +18966,7 @@
         <v>51.96</v>
       </c>
     </row>
-    <row r="182" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>218</v>
       </c>
@@ -19044,7 +19043,7 @@
         <v>113367.97</v>
       </c>
     </row>
-    <row r="183" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>218</v>
       </c>
@@ -19121,7 +19120,7 @@
         <v>54501</v>
       </c>
     </row>
-    <row r="184" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>218</v>
       </c>
@@ -19198,7 +19197,7 @@
         <v>42180</v>
       </c>
     </row>
-    <row r="185" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>218</v>
       </c>
@@ -19275,7 +19274,7 @@
         <v>3600</v>
       </c>
     </row>
-    <row r="186" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>218</v>
       </c>
@@ -19352,7 +19351,7 @@
         <v>10775</v>
       </c>
     </row>
-    <row r="187" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>218</v>
       </c>
@@ -19429,7 +19428,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="188" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>218</v>
       </c>
@@ -19506,7 +19505,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="189" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>225</v>
       </c>
@@ -19581,7 +19580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="190" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>225</v>
       </c>
@@ -19658,7 +19657,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>225</v>
       </c>
@@ -19733,7 +19732,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="192" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>225</v>
       </c>
@@ -19810,7 +19809,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="193" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>225</v>
       </c>
@@ -19887,7 +19886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="194" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>225</v>
       </c>
@@ -19964,7 +19963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>225</v>
       </c>
@@ -20041,7 +20040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>239</v>
       </c>
@@ -20118,7 +20117,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="197" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>239</v>
       </c>
@@ -20195,7 +20194,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="198" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>239</v>
       </c>
@@ -20272,7 +20271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="199" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>239</v>
       </c>
@@ -20347,7 +20346,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="200" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>239</v>
       </c>
@@ -20424,7 +20423,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="201" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>239</v>
       </c>
@@ -20501,7 +20500,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="202" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>241</v>
       </c>
@@ -20570,7 +20569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="203" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>434</v>
       </c>
@@ -20645,7 +20644,7 @@
         <v>2072.4699999999998</v>
       </c>
     </row>
-    <row r="204" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>434</v>
       </c>
@@ -20722,7 +20721,7 @@
         <v>2071.7199999999998</v>
       </c>
     </row>
-    <row r="205" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>434</v>
       </c>
@@ -20799,7 +20798,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="206" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>434</v>
       </c>
@@ -20876,7 +20875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="207" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>434</v>
       </c>
@@ -20953,7 +20952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>434</v>
       </c>
@@ -21030,7 +21029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>434</v>
       </c>
@@ -21107,7 +21106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>436</v>
       </c>
@@ -21184,7 +21183,7 @@
         <v>9.1999999999999993</v>
       </c>
     </row>
-    <row r="211" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>436</v>
       </c>
@@ -21261,7 +21260,7 @@
         <v>6.1</v>
       </c>
     </row>
-    <row r="212" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>436</v>
       </c>
@@ -21338,7 +21337,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="213" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>485</v>
       </c>
@@ -21411,7 +21410,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="214" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>485</v>
       </c>
@@ -21483,7 +21482,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="215" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>485</v>
       </c>
@@ -21557,7 +21556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="216" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>485</v>
       </c>
@@ -21631,7 +21630,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="217" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>485</v>
       </c>
@@ -21705,7 +21704,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="218" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>485</v>
       </c>
@@ -21779,7 +21778,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="219" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>485</v>
       </c>
@@ -21853,7 +21852,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="220" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>485</v>
       </c>
@@ -21927,7 +21926,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="221" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>485</v>
       </c>
@@ -22001,7 +22000,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="222" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>485</v>
       </c>
@@ -22075,7 +22074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="223" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>488</v>
       </c>
@@ -22150,7 +22149,7 @@
         <v>78.048780487804876</v>
       </c>
     </row>
-    <row r="224" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>488</v>
       </c>
@@ -22224,7 +22223,7 @@
         <v>78.790000000000006</v>
       </c>
     </row>
-    <row r="225" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>488</v>
       </c>
@@ -22298,7 +22297,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="226" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>488</v>
       </c>
@@ -22372,7 +22371,7 @@
         <v>82.61</v>
       </c>
     </row>
-    <row r="227" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>488</v>
       </c>
@@ -22446,7 +22445,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="228" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>488</v>
       </c>
@@ -22520,7 +22519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="229" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>488</v>
       </c>
@@ -22594,7 +22593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="230" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>488</v>
       </c>
@@ -22668,7 +22667,7 @@
         <v>79.03</v>
       </c>
     </row>
-    <row r="231" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>488</v>
       </c>
@@ -22742,7 +22741,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="232" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>488</v>
       </c>
@@ -22816,7 +22815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="233" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>509</v>
       </c>
@@ -22877,7 +22876,7 @@
         <v>99.45</v>
       </c>
     </row>
-    <row r="234" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>509</v>
       </c>
@@ -22951,7 +22950,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="235" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>509</v>
       </c>
@@ -23025,7 +23024,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="236" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>509</v>
       </c>
@@ -23099,7 +23098,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="237" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>509</v>
       </c>
@@ -23173,7 +23172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="238" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>509</v>
       </c>
@@ -23247,7 +23246,7 @@
         <v>98.77</v>
       </c>
     </row>
-    <row r="239" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>509</v>
       </c>
@@ -23321,7 +23320,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="240" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>509</v>
       </c>
@@ -23395,7 +23394,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="241" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>509</v>
       </c>
@@ -23469,7 +23468,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="242" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>509</v>
       </c>
@@ -23543,7 +23542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="243" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>509</v>
       </c>
@@ -23617,7 +23616,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="244" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>509</v>
       </c>
@@ -23691,7 +23690,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="245" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>509</v>
       </c>
@@ -23765,7 +23764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="246" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>509</v>
       </c>
@@ -23839,7 +23838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="247" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>509</v>
       </c>
@@ -23913,7 +23912,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="248" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>509</v>
       </c>
@@ -23987,7 +23986,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="249" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>509</v>
       </c>
@@ -24061,7 +24060,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="250" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>509</v>
       </c>
@@ -24135,7 +24134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="251" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>509</v>
       </c>
@@ -24209,7 +24208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="252" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>68</v>
       </c>
@@ -24284,7 +24283,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="253" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>73</v>
       </c>
@@ -24361,7 +24360,7 @@
         <v>18.41</v>
       </c>
     </row>
-    <row r="254" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>74</v>
       </c>
@@ -24438,7 +24437,7 @@
         <v>80.327868852459019</v>
       </c>
     </row>
-    <row r="255" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>86</v>
       </c>
@@ -24515,7 +24514,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="256" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>95</v>
       </c>
@@ -24592,7 +24591,7 @@
         <v>33.333333333333329</v>
       </c>
     </row>
-    <row r="257" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>143</v>
       </c>
@@ -24669,7 +24668,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="258" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>145</v>
       </c>
@@ -24746,7 +24745,7 @@
         <v>1.545454545454545</v>
       </c>
     </row>
-    <row r="259" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>146</v>
       </c>
@@ -24823,7 +24822,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="260" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>148</v>
       </c>
@@ -24900,7 +24899,7 @@
         <v>1.977873977873978</v>
       </c>
     </row>
-    <row r="261" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>159</v>
       </c>
@@ -24950,7 +24949,7 @@
         <v>97.8</v>
       </c>
     </row>
-    <row r="262" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>167</v>
       </c>
@@ -25021,7 +25020,7 @@
       <c r="X262" s="3"/>
       <c r="Y262" s="3"/>
     </row>
-    <row r="263" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>193</v>
       </c>
@@ -25086,7 +25085,7 @@
       <c r="X263" s="3"/>
       <c r="Y263" s="3"/>
     </row>
-    <row r="264" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>199</v>
       </c>
@@ -25155,7 +25154,7 @@
       <c r="X264" s="3"/>
       <c r="Y264" s="3"/>
     </row>
-    <row r="265" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>203</v>
       </c>
@@ -25232,7 +25231,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="266" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>203</v>
       </c>
@@ -25309,7 +25308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="267" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>203</v>
       </c>
@@ -25386,7 +25385,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="268" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>203</v>
       </c>
@@ -25463,7 +25462,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="269" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>204</v>
       </c>
@@ -25528,7 +25527,7 @@
       <c r="X269" s="3"/>
       <c r="Y269" s="3"/>
     </row>
-    <row r="270" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>205</v>
       </c>
@@ -25593,7 +25592,7 @@
       <c r="X270" s="3"/>
       <c r="Y270" s="3"/>
     </row>
-    <row r="271" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>207</v>
       </c>
@@ -25658,7 +25657,7 @@
       <c r="X271" s="3"/>
       <c r="Y271" s="3"/>
     </row>
-    <row r="272" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>215</v>
       </c>
@@ -25735,7 +25734,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="273" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>215</v>
       </c>
@@ -25812,7 +25811,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="274" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>215</v>
       </c>
@@ -25889,7 +25888,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="275" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>215</v>
       </c>
@@ -25966,7 +25965,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="276" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>215</v>
       </c>
@@ -26043,7 +26042,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="277" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>215</v>
       </c>
@@ -26120,7 +26119,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="278" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>215</v>
       </c>
@@ -26197,7 +26196,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="279" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>219</v>
       </c>
@@ -26272,7 +26271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="280" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>219</v>
       </c>
@@ -26349,7 +26348,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="281" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>219</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="282" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>219</v>
       </c>
@@ -26503,7 +26502,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="283" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>219</v>
       </c>
@@ -26580,7 +26579,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="284" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>219</v>
       </c>
@@ -26657,7 +26656,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="285" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>219</v>
       </c>
@@ -26734,7 +26733,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="286" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>219</v>
       </c>
@@ -26792,7 +26791,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="287" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>220</v>
       </c>
@@ -26867,7 +26866,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="288" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>220</v>
       </c>
@@ -26944,7 +26943,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="289" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>220</v>
       </c>
@@ -27021,7 +27020,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="290" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>220</v>
       </c>
@@ -27098,7 +27097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="291" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>220</v>
       </c>
@@ -27175,7 +27174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="292" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>220</v>
       </c>
@@ -27248,7 +27247,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="293" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>220</v>
       </c>
@@ -27325,7 +27324,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="294" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>230</v>
       </c>
@@ -27388,7 +27387,7 @@
       <c r="X294" s="3"/>
       <c r="Y294" s="3"/>
     </row>
-    <row r="295" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>231</v>
       </c>
@@ -27451,7 +27450,7 @@
       <c r="X295" s="3"/>
       <c r="Y295" s="3"/>
     </row>
-    <row r="296" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>232</v>
       </c>
@@ -27514,7 +27513,7 @@
       <c r="X296" s="3"/>
       <c r="Y296" s="3"/>
     </row>
-    <row r="297" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -27579,7 +27578,7 @@
       <c r="X297" s="3"/>
       <c r="Y297" s="3"/>
     </row>
-    <row r="298" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>246</v>
       </c>
@@ -27642,7 +27641,7 @@
       <c r="X298" s="3"/>
       <c r="Y298" s="3"/>
     </row>
-    <row r="299" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>252</v>
       </c>
@@ -27707,7 +27706,7 @@
       <c r="X299" s="3"/>
       <c r="Y299" s="3"/>
     </row>
-    <row r="300" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>256</v>
       </c>
@@ -27770,7 +27769,7 @@
       <c r="X300" s="3"/>
       <c r="Y300" s="3"/>
     </row>
-    <row r="301" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>260</v>
       </c>
@@ -27835,7 +27834,7 @@
       <c r="X301" s="3"/>
       <c r="Y301" s="3"/>
     </row>
-    <row r="302" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>261</v>
       </c>
@@ -27900,7 +27899,7 @@
       <c r="X302" s="3"/>
       <c r="Y302" s="3"/>
     </row>
-    <row r="303" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>262</v>
       </c>
@@ -27963,7 +27962,7 @@
       <c r="X303" s="3"/>
       <c r="Y303" s="3"/>
     </row>
-    <row r="304" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>268</v>
       </c>
@@ -28028,7 +28027,7 @@
       <c r="X304" s="3"/>
       <c r="Y304" s="3"/>
     </row>
-    <row r="305" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>269</v>
       </c>
@@ -28093,7 +28092,7 @@
       <c r="X305" s="3"/>
       <c r="Y305" s="3"/>
     </row>
-    <row r="306" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>270</v>
       </c>
@@ -28158,7 +28157,7 @@
       <c r="X306" s="3"/>
       <c r="Y306" s="3"/>
     </row>
-    <row r="307" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>271</v>
       </c>
@@ -28223,7 +28222,7 @@
       <c r="X307" s="3"/>
       <c r="Y307" s="3"/>
     </row>
-    <row r="308" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>273</v>
       </c>
@@ -28288,7 +28287,7 @@
       <c r="X308" s="3"/>
       <c r="Y308" s="3"/>
     </row>
-    <row r="309" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>274</v>
       </c>
@@ -28365,7 +28364,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="310" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>274</v>
       </c>
@@ -28442,7 +28441,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="311" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>274</v>
       </c>
@@ -28519,7 +28518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="312" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>274</v>
       </c>
@@ -28596,7 +28595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="313" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>274</v>
       </c>
@@ -28673,7 +28672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="314" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>275</v>
       </c>
@@ -28750,7 +28749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="315" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>275</v>
       </c>
@@ -28827,7 +28826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="316" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>275</v>
       </c>
@@ -28904,7 +28903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="317" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>275</v>
       </c>
@@ -28981,7 +28980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="318" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>276</v>
       </c>
@@ -29046,7 +29045,7 @@
       <c r="X318" s="3"/>
       <c r="Y318" s="3"/>
     </row>
-    <row r="319" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>277</v>
       </c>
@@ -29111,7 +29110,7 @@
       <c r="X319" s="3"/>
       <c r="Y319" s="3"/>
     </row>
-    <row r="320" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>278</v>
       </c>
@@ -29188,7 +29187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>278</v>
       </c>
@@ -29265,7 +29264,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="322" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>278</v>
       </c>
@@ -29342,7 +29341,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="323" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>278</v>
       </c>
@@ -29419,7 +29418,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="324" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>282</v>
       </c>
@@ -29484,7 +29483,7 @@
       <c r="X324" s="3"/>
       <c r="Y324" s="3"/>
     </row>
-    <row r="325" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>283</v>
       </c>
@@ -29549,7 +29548,7 @@
       <c r="X325" s="3"/>
       <c r="Y325" s="3"/>
     </row>
-    <row r="326" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>285</v>
       </c>
@@ -29614,7 +29613,7 @@
       <c r="X326" s="3"/>
       <c r="Y326" s="3"/>
     </row>
-    <row r="327" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>286</v>
       </c>
@@ -29691,7 +29690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>286</v>
       </c>
@@ -29768,7 +29767,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="329" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>286</v>
       </c>
@@ -29845,7 +29844,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="330" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>286</v>
       </c>
@@ -29922,7 +29921,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="331" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>286</v>
       </c>
@@ -29999,7 +29998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="332" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>292</v>
       </c>
@@ -30076,7 +30075,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="333" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>292</v>
       </c>
@@ -30153,7 +30152,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="334" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>292</v>
       </c>
@@ -30230,7 +30229,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="335" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>292</v>
       </c>
@@ -30307,7 +30306,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="336" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>294</v>
       </c>
@@ -30384,7 +30383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="337" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>294</v>
       </c>
@@ -30461,7 +30460,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="338" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>294</v>
       </c>
@@ -30538,7 +30537,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="339" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>294</v>
       </c>
@@ -30615,7 +30614,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="340" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>302</v>
       </c>
@@ -30692,7 +30691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>302</v>
       </c>
@@ -30769,7 +30768,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="342" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>302</v>
       </c>
@@ -30846,7 +30845,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="343" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>302</v>
       </c>
@@ -30923,7 +30922,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="344" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>302</v>
       </c>
@@ -31000,7 +30999,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="345" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>303</v>
       </c>
@@ -31075,7 +31074,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="346" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>303</v>
       </c>
@@ -31152,7 +31151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="347" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>303</v>
       </c>
@@ -31229,7 +31228,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="348" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>303</v>
       </c>
@@ -31306,7 +31305,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="349" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>304</v>
       </c>
@@ -31371,7 +31370,7 @@
       <c r="X349" s="3"/>
       <c r="Y349" s="3"/>
     </row>
-    <row r="350" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>323</v>
       </c>
@@ -31436,7 +31435,7 @@
       <c r="X350" s="3"/>
       <c r="Y350" s="3"/>
     </row>
-    <row r="351" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>324</v>
       </c>
@@ -31501,7 +31500,7 @@
       <c r="X351" s="3"/>
       <c r="Y351" s="3"/>
     </row>
-    <row r="352" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>325</v>
       </c>
@@ -31566,7 +31565,7 @@
       <c r="X352" s="3"/>
       <c r="Y352" s="3"/>
     </row>
-    <row r="353" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>327</v>
       </c>
@@ -31631,7 +31630,7 @@
       <c r="X353" s="3"/>
       <c r="Y353" s="3"/>
     </row>
-    <row r="354" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>332</v>
       </c>
@@ -31696,7 +31695,7 @@
       <c r="X354" s="3"/>
       <c r="Y354" s="3"/>
     </row>
-    <row r="355" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>337</v>
       </c>
@@ -31761,7 +31760,7 @@
       <c r="X355" s="3"/>
       <c r="Y355" s="3"/>
     </row>
-    <row r="356" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>338</v>
       </c>
@@ -31826,7 +31825,7 @@
       <c r="X356" s="3"/>
       <c r="Y356" s="3"/>
     </row>
-    <row r="357" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>341</v>
       </c>
@@ -31891,7 +31890,7 @@
       <c r="X357" s="3"/>
       <c r="Y357" s="3"/>
     </row>
-    <row r="358" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>344</v>
       </c>
@@ -31956,7 +31955,7 @@
       <c r="X358" s="3"/>
       <c r="Y358" s="3"/>
     </row>
-    <row r="359" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>356</v>
       </c>
@@ -32021,7 +32020,7 @@
       <c r="X359" s="3"/>
       <c r="Y359" s="3"/>
     </row>
-    <row r="360" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>357</v>
       </c>
@@ -32082,7 +32081,7 @@
       <c r="X360" s="3"/>
       <c r="Y360" s="3"/>
     </row>
-    <row r="361" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>358</v>
       </c>
@@ -32147,7 +32146,7 @@
       <c r="X361" s="3"/>
       <c r="Y361" s="3"/>
     </row>
-    <row r="362" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>359</v>
       </c>
@@ -32208,7 +32207,7 @@
       <c r="X362" s="3"/>
       <c r="Y362" s="3"/>
     </row>
-    <row r="363" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>362</v>
       </c>
@@ -32285,7 +32284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="364" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>362</v>
       </c>
@@ -32362,7 +32361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="365" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>362</v>
       </c>
@@ -32439,7 +32438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="366" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>363</v>
       </c>
@@ -32502,7 +32501,7 @@
       <c r="X366" s="3"/>
       <c r="Y366" s="3"/>
     </row>
-    <row r="367" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>364</v>
       </c>
@@ -32567,7 +32566,7 @@
       <c r="X367" s="3"/>
       <c r="Y367" s="3"/>
     </row>
-    <row r="368" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>369</v>
       </c>
@@ -32644,7 +32643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>369</v>
       </c>
@@ -32721,7 +32720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="370" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -32798,7 +32797,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="371" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>371</v>
       </c>
@@ -32863,7 +32862,7 @@
       <c r="X371" s="3"/>
       <c r="Y371" s="3"/>
     </row>
-    <row r="372" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>375</v>
       </c>
@@ -32940,7 +32939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>375</v>
       </c>
@@ -33017,7 +33016,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="374" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>375</v>
       </c>
@@ -33094,7 +33093,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="375" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>376</v>
       </c>
@@ -33159,7 +33158,7 @@
       <c r="X375" s="3"/>
       <c r="Y375" s="3"/>
     </row>
-    <row r="376" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>379</v>
       </c>
@@ -33224,7 +33223,7 @@
       <c r="X376" s="3"/>
       <c r="Y376" s="3"/>
     </row>
-    <row r="377" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>381</v>
       </c>
@@ -33289,7 +33288,7 @@
       <c r="X377" s="3"/>
       <c r="Y377" s="3"/>
     </row>
-    <row r="378" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>382</v>
       </c>
@@ -33354,7 +33353,7 @@
       <c r="X378" s="3"/>
       <c r="Y378" s="3"/>
     </row>
-    <row r="379" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>383</v>
       </c>
@@ -33419,7 +33418,7 @@
       <c r="X379" s="3"/>
       <c r="Y379" s="3"/>
     </row>
-    <row r="380" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>384</v>
       </c>
@@ -33484,7 +33483,7 @@
       <c r="X380" s="3"/>
       <c r="Y380" s="3"/>
     </row>
-    <row r="381" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>385</v>
       </c>
@@ -33549,7 +33548,7 @@
       <c r="X381" s="3"/>
       <c r="Y381" s="3"/>
     </row>
-    <row r="382" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>386</v>
       </c>
@@ -33626,7 +33625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="383" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>386</v>
       </c>
@@ -33703,7 +33702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="384" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>386</v>
       </c>
@@ -33780,7 +33779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="385" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>386</v>
       </c>
@@ -33857,7 +33856,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="386" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>389</v>
       </c>
@@ -33930,7 +33929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>389</v>
       </c>
@@ -34004,7 +34003,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="388" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>389</v>
       </c>
@@ -34078,7 +34077,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="389" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>389</v>
       </c>
@@ -34152,7 +34151,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="390" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -34226,7 +34225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="391" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>389</v>
       </c>
@@ -34300,7 +34299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="392" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>389</v>
       </c>
@@ -34374,7 +34373,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="393" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>389</v>
       </c>
@@ -34448,7 +34447,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="394" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>389</v>
       </c>
@@ -34522,7 +34521,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="395" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>389</v>
       </c>
@@ -34596,7 +34595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="396" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>389</v>
       </c>
@@ -34670,7 +34669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="397" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>389</v>
       </c>
@@ -34744,7 +34743,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="398" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>389</v>
       </c>
@@ -34818,7 +34817,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="399" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -34883,7 +34882,7 @@
       <c r="X399" s="3"/>
       <c r="Y399" s="3"/>
     </row>
-    <row r="400" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>398</v>
       </c>
@@ -34948,7 +34947,7 @@
       <c r="X400" s="3"/>
       <c r="Y400" s="3"/>
     </row>
-    <row r="401" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -35013,7 +35012,7 @@
       <c r="X401" s="3"/>
       <c r="Y401" s="3"/>
     </row>
-    <row r="402" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>400</v>
       </c>
@@ -35078,7 +35077,7 @@
       <c r="X402" s="3"/>
       <c r="Y402" s="3"/>
     </row>
-    <row r="403" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -35143,7 +35142,7 @@
       <c r="X403" s="3"/>
       <c r="Y403" s="3"/>
     </row>
-    <row r="404" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>403</v>
       </c>
@@ -35208,7 +35207,7 @@
       <c r="X404" s="3"/>
       <c r="Y404" s="3"/>
     </row>
-    <row r="405" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>408</v>
       </c>
@@ -35285,7 +35284,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="406" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>408</v>
       </c>
@@ -35362,7 +35361,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="407" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>408</v>
       </c>
@@ -35439,7 +35438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="408" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>408</v>
       </c>
@@ -35516,7 +35515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="409" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>422</v>
       </c>
@@ -35581,7 +35580,7 @@
       <c r="X409" s="3"/>
       <c r="Y409" s="3"/>
     </row>
-    <row r="410" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>426</v>
       </c>
@@ -35640,7 +35639,7 @@
       <c r="X410" s="3"/>
       <c r="Y410" s="3"/>
     </row>
-    <row r="411" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>427</v>
       </c>
@@ -35717,7 +35716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>427</v>
       </c>
@@ -35794,7 +35793,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="413" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>427</v>
       </c>
@@ -35871,7 +35870,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="414" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>427</v>
       </c>
@@ -35948,7 +35947,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="415" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>427</v>
       </c>
@@ -36025,7 +36024,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="416" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>427</v>
       </c>
@@ -36098,7 +36097,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="417" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>427</v>
       </c>
@@ -36175,7 +36174,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="418" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>428</v>
       </c>
@@ -36252,7 +36251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="419" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>428</v>
       </c>
@@ -36329,7 +36328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="420" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>428</v>
       </c>
@@ -36406,7 +36405,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="421" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>428</v>
       </c>
@@ -36481,7 +36480,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="422" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>428</v>
       </c>
@@ -36558,7 +36557,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="423" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>428</v>
       </c>
@@ -36631,7 +36630,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="424" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>428</v>
       </c>
@@ -36706,7 +36705,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="425" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>428</v>
       </c>
@@ -36760,7 +36759,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="426" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>429</v>
       </c>
@@ -36837,7 +36836,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="427" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>429</v>
       </c>
@@ -36914,7 +36913,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="428" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>429</v>
       </c>
@@ -36991,7 +36990,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="429" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>429</v>
       </c>
@@ -37068,7 +37067,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="430" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -37145,7 +37144,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="431" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>429</v>
       </c>
@@ -37222,7 +37221,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="432" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>429</v>
       </c>
@@ -37299,7 +37298,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="433" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>430</v>
       </c>
@@ -37376,7 +37375,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="434" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>430</v>
       </c>
@@ -37453,7 +37452,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="435" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>430</v>
       </c>
@@ -37530,7 +37529,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="436" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>430</v>
       </c>
@@ -37607,7 +37606,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="437" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>430</v>
       </c>
@@ -37684,7 +37683,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="438" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>433</v>
       </c>
@@ -37761,7 +37760,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="439" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>433</v>
       </c>
@@ -37838,7 +37837,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="440" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>433</v>
       </c>
@@ -37915,7 +37914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="441" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>433</v>
       </c>
@@ -37992,7 +37991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="442" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>433</v>
       </c>
@@ -38065,7 +38064,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="443" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>433</v>
       </c>
@@ -38136,7 +38135,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="444" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>433</v>
       </c>
@@ -38211,7 +38210,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="445" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>433</v>
       </c>
@@ -38269,7 +38268,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="446" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>435</v>
       </c>
@@ -38344,7 +38343,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="447" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>435</v>
       </c>
@@ -38421,7 +38420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="448" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>435</v>
       </c>
@@ -38498,7 +38497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="449" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>435</v>
       </c>
@@ -38575,7 +38574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="450" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>435</v>
       </c>
@@ -38652,7 +38651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="451" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>435</v>
       </c>
@@ -38729,7 +38728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="452" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>435</v>
       </c>
@@ -38806,7 +38805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="453" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>439</v>
       </c>
@@ -38883,7 +38882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>439</v>
       </c>
@@ -38960,7 +38959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="455" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>439</v>
       </c>
@@ -39037,7 +39036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="456" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>440</v>
       </c>
@@ -39114,7 +39113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="457" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>440</v>
       </c>
@@ -39191,7 +39190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="458" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>440</v>
       </c>
@@ -39268,7 +39267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="459" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>444</v>
       </c>
@@ -39327,7 +39326,7 @@
       <c r="X459" s="3"/>
       <c r="Y459" s="3"/>
     </row>
-    <row r="460" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>445</v>
       </c>
@@ -39388,7 +39387,7 @@
       <c r="X460" s="3"/>
       <c r="Y460" s="3"/>
     </row>
-    <row r="461" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>447</v>
       </c>
@@ -39449,7 +39448,7 @@
       <c r="X461" s="3"/>
       <c r="Y461" s="3"/>
     </row>
-    <row r="462" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>448</v>
       </c>
@@ -39510,7 +39509,7 @@
       <c r="X462" s="3"/>
       <c r="Y462" s="3"/>
     </row>
-    <row r="463" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>451</v>
       </c>
@@ -39571,7 +39570,7 @@
       <c r="X463" s="3"/>
       <c r="Y463" s="3"/>
     </row>
-    <row r="464" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>452</v>
       </c>
@@ -39628,7 +39627,7 @@
       <c r="X464" s="3"/>
       <c r="Y464" s="3"/>
     </row>
-    <row r="465" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>466</v>
       </c>
@@ -39689,7 +39688,7 @@
       <c r="X465" s="3"/>
       <c r="Y465" s="3"/>
     </row>
-    <row r="466" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>467</v>
       </c>
@@ -39750,7 +39749,7 @@
       <c r="X466" s="3"/>
       <c r="Y466" s="3"/>
     </row>
-    <row r="467" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>468</v>
       </c>
@@ -39811,7 +39810,7 @@
       <c r="X467" s="3"/>
       <c r="Y467" s="3"/>
     </row>
-    <row r="468" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>473</v>
       </c>
@@ -39888,7 +39887,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="469" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>473</v>
       </c>
@@ -39965,7 +39964,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="470" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>473</v>
       </c>
@@ -40042,7 +40041,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="471" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>473</v>
       </c>
@@ -40119,7 +40118,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="472" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>474</v>
       </c>
@@ -40192,7 +40191,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="473" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>474</v>
       </c>
@@ -40266,7 +40265,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="474" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>474</v>
       </c>
@@ -40340,7 +40339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="475" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -40414,7 +40413,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="476" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>474</v>
       </c>
@@ -40488,7 +40487,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="477" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>474</v>
       </c>
@@ -40562,7 +40561,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="478" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>474</v>
       </c>
@@ -40636,7 +40635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="479" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>474</v>
       </c>
@@ -40710,7 +40709,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="480" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>474</v>
       </c>
@@ -40784,7 +40783,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="481" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>474</v>
       </c>
@@ -40858,7 +40857,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="482" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>474</v>
       </c>
@@ -40932,7 +40931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="483" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>474</v>
       </c>
@@ -41006,7 +41005,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="484" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>474</v>
       </c>
@@ -41080,7 +41079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="485" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>475</v>
       </c>
@@ -41141,7 +41140,7 @@
       <c r="X485" s="3"/>
       <c r="Y485" s="3"/>
     </row>
-    <row r="486" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>476</v>
       </c>
@@ -41218,7 +41217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>476</v>
       </c>
@@ -41295,7 +41294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="488" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>476</v>
       </c>
@@ -41372,7 +41371,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="489" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>476</v>
       </c>
@@ -41449,7 +41448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="490" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>477</v>
       </c>
@@ -41520,7 +41519,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="491" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>477</v>
       </c>
@@ -41594,7 +41593,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="492" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>477</v>
       </c>
@@ -41668,7 +41667,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="493" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>477</v>
       </c>
@@ -41742,7 +41741,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="494" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>477</v>
       </c>
@@ -41816,7 +41815,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="495" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>477</v>
       </c>
@@ -41890,7 +41889,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="496" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>477</v>
       </c>
@@ -41964,7 +41963,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="497" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>477</v>
       </c>
@@ -42038,7 +42037,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="498" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>477</v>
       </c>
@@ -42112,7 +42111,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="499" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>477</v>
       </c>
@@ -42186,7 +42185,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="500" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>477</v>
       </c>
@@ -42260,7 +42259,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="501" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>477</v>
       </c>
@@ -42334,7 +42333,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="502" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>477</v>
       </c>
@@ -42408,7 +42407,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="503" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>478</v>
       </c>
@@ -42481,7 +42480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>478</v>
       </c>
@@ -42555,7 +42554,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="505" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>478</v>
       </c>
@@ -42629,7 +42628,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="506" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>478</v>
       </c>
@@ -42703,7 +42702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="507" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>478</v>
       </c>
@@ -42777,7 +42776,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="508" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>478</v>
       </c>
@@ -42851,7 +42850,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="509" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>478</v>
       </c>
@@ -42925,7 +42924,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="510" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>478</v>
       </c>
@@ -42999,7 +42998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="511" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>478</v>
       </c>
@@ -43073,7 +43072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="512" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>478</v>
       </c>
@@ -43147,7 +43146,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="513" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>478</v>
       </c>
@@ -43221,7 +43220,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="514" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>478</v>
       </c>
@@ -43295,7 +43294,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="515" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>478</v>
       </c>
@@ -43369,7 +43368,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="516" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>479</v>
       </c>
@@ -43442,7 +43441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>479</v>
       </c>
@@ -43519,7 +43518,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="518" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>479</v>
       </c>
@@ -43596,7 +43595,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="519" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>479</v>
       </c>
@@ -43673,7 +43672,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="520" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>479</v>
       </c>
@@ -43750,7 +43749,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="521" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>479</v>
       </c>
@@ -43827,7 +43826,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="522" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>479</v>
       </c>
@@ -43904,7 +43903,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="523" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>479</v>
       </c>
@@ -43981,7 +43980,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="524" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>479</v>
       </c>
@@ -44058,7 +44057,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="525" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>479</v>
       </c>
@@ -44135,7 +44134,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="526" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>479</v>
       </c>
@@ -44212,7 +44211,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="527" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>479</v>
       </c>
@@ -44289,7 +44288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="528" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>479</v>
       </c>
@@ -44366,7 +44365,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="529" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>480</v>
       </c>
@@ -44439,7 +44438,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="530" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>480</v>
       </c>
@@ -44516,7 +44515,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="531" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>480</v>
       </c>
@@ -44593,7 +44592,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="532" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>480</v>
       </c>
@@ -44670,7 +44669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="533" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>480</v>
       </c>
@@ -44747,7 +44746,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="534" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>480</v>
       </c>
@@ -44824,7 +44823,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="535" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>480</v>
       </c>
@@ -44901,7 +44900,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="536" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>480</v>
       </c>
@@ -44978,7 +44977,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="537" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>480</v>
       </c>
@@ -45055,7 +45054,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="538" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>480</v>
       </c>
@@ -45132,7 +45131,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="539" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>480</v>
       </c>
@@ -45209,7 +45208,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="540" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>480</v>
       </c>
@@ -45286,7 +45285,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="541" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>480</v>
       </c>
@@ -45363,7 +45362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="542" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>481</v>
       </c>
@@ -45424,7 +45423,7 @@
       <c r="X542" s="3"/>
       <c r="Y542" s="3"/>
     </row>
-    <row r="543" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>481</v>
       </c>
@@ -45494,7 +45493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="544" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>486</v>
       </c>
@@ -45553,7 +45552,7 @@
       <c r="X544" s="3"/>
       <c r="Y544" s="3"/>
     </row>
-    <row r="545" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>506</v>
       </c>
@@ -45612,7 +45611,7 @@
       <c r="X545" s="3"/>
       <c r="Y545" s="3"/>
     </row>
-    <row r="546" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>507</v>
       </c>
@@ -45671,7 +45670,7 @@
       <c r="X546" s="3"/>
       <c r="Y546" s="3"/>
     </row>
-    <row r="547" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>514</v>
       </c>
@@ -45728,7 +45727,7 @@
       <c r="X547" s="3"/>
       <c r="Y547" s="3"/>
     </row>
-    <row r="548" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>515</v>
       </c>
@@ -45783,7 +45782,7 @@
       <c r="X548" s="3"/>
       <c r="Y548" s="3"/>
     </row>
-    <row r="549" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>516</v>
       </c>
@@ -45838,7 +45837,7 @@
       <c r="X549" s="3"/>
       <c r="Y549" s="3"/>
     </row>
-    <row r="550" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>519</v>
       </c>
@@ -45915,7 +45914,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="551" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>519</v>
       </c>
@@ -45992,7 +45991,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="552" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>519</v>
       </c>
@@ -46069,7 +46068,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="553" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>523</v>
       </c>
@@ -46146,7 +46145,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="554" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>523</v>
       </c>
@@ -46223,7 +46222,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="555" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>523</v>
       </c>
@@ -46300,7 +46299,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="556" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>523</v>
       </c>
@@ -46377,7 +46376,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="557" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>524</v>
       </c>
@@ -46454,7 +46453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="558" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>524</v>
       </c>
@@ -46531,7 +46530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="559" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>524</v>
       </c>
@@ -46608,7 +46607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="560" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>524</v>
       </c>
@@ -46685,7 +46684,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="561" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>524</v>
       </c>
@@ -46762,7 +46761,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="562" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>524</v>
       </c>
@@ -46839,7 +46838,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="563" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>524</v>
       </c>
@@ -46916,7 +46915,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="564" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>530</v>
       </c>
@@ -46971,7 +46970,7 @@
       <c r="X564" s="3"/>
       <c r="Y564" s="3"/>
     </row>
-    <row r="565" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>531</v>
       </c>
@@ -47026,7 +47025,7 @@
       <c r="X565" s="3"/>
       <c r="Y565" s="3"/>
     </row>
-    <row r="566" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>532</v>
       </c>
@@ -47095,7 +47094,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="567" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>532</v>
       </c>
@@ -47172,7 +47171,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="568" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>532</v>
       </c>
@@ -47249,7 +47248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="569" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>532</v>
       </c>
@@ -47326,7 +47325,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="570" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>532</v>
       </c>
@@ -47403,7 +47402,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="571" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>533</v>
       </c>
@@ -47480,7 +47479,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="572" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>533</v>
       </c>
@@ -47557,7 +47556,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>533</v>
       </c>
@@ -47634,7 +47633,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="574" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>534</v>
       </c>
@@ -47711,7 +47710,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="575" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>534</v>
       </c>
@@ -47788,7 +47787,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="576" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>534</v>
       </c>
@@ -47865,7 +47864,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="577" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>535</v>
       </c>
@@ -47942,7 +47941,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="578" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>535</v>
       </c>
@@ -48019,7 +48018,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="579" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>535</v>
       </c>
@@ -48096,7 +48095,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="580" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>536</v>
       </c>
@@ -48173,7 +48172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="581" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>536</v>
       </c>
@@ -48250,7 +48249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="582" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>536</v>
       </c>
@@ -48327,7 +48326,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="583" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>537</v>
       </c>
@@ -48384,7 +48383,7 @@
       <c r="X583" s="3"/>
       <c r="Y583" s="3"/>
     </row>
-    <row r="584" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>538</v>
       </c>
@@ -48439,7 +48438,7 @@
       <c r="X584" s="3"/>
       <c r="Y584" s="3"/>
     </row>
-    <row r="585" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>539</v>
       </c>
@@ -48494,7 +48493,7 @@
       <c r="X585" s="3"/>
       <c r="Y585" s="3"/>
     </row>
-    <row r="586" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>540</v>
       </c>
@@ -48551,7 +48550,7 @@
       <c r="X586" s="3"/>
       <c r="Y586" s="3"/>
     </row>
-    <row r="587" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>543</v>
       </c>
@@ -48626,7 +48625,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="588" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>543</v>
       </c>
@@ -48703,7 +48702,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="589" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>543</v>
       </c>
@@ -48780,7 +48779,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="590" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>544</v>
       </c>
@@ -48855,7 +48854,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="591" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>544</v>
       </c>
@@ -48932,7 +48931,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="592" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>544</v>
       </c>
@@ -49009,7 +49008,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="593" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>544</v>
       </c>
@@ -49086,7 +49085,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="594" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>544</v>
       </c>
@@ -49163,7 +49162,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="595" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>550</v>
       </c>
@@ -49220,7 +49219,7 @@
       <c r="X595" s="3"/>
       <c r="Y595" s="3"/>
     </row>
-    <row r="596" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>551</v>
       </c>
@@ -49277,7 +49276,7 @@
       <c r="X596" s="3"/>
       <c r="Y596" s="3"/>
     </row>
-    <row r="597" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>554</v>
       </c>
@@ -49332,7 +49331,7 @@
       <c r="X597" s="3"/>
       <c r="Y597" s="3"/>
     </row>
-    <row r="598" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>555</v>
       </c>
@@ -49387,7 +49386,7 @@
       <c r="X598" s="3"/>
       <c r="Y598" s="3"/>
     </row>
-    <row r="599" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>69</v>
       </c>
@@ -49464,7 +49463,7 @@
         <v>90.541781450871994</v>
       </c>
     </row>
-    <row r="600" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>111</v>
       </c>
@@ -49541,7 +49540,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="601" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>197</v>
       </c>
@@ -49618,7 +49617,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="602" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>213</v>
       </c>
@@ -49695,7 +49694,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="603" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>213</v>
       </c>
@@ -49772,7 +49771,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="604" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>213</v>
       </c>
@@ -49849,7 +49848,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="605" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>213</v>
       </c>
@@ -49926,7 +49925,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="606" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>213</v>
       </c>
@@ -50003,7 +50002,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="607" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>213</v>
       </c>
@@ -50080,7 +50079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="608" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>213</v>
       </c>
@@ -50157,7 +50156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="609" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>213</v>
       </c>
@@ -50234,7 +50233,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="610" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>213</v>
       </c>
@@ -50311,7 +50310,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="611" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>233</v>
       </c>
@@ -50386,7 +50385,7 @@
         <v>64.367816091954026</v>
       </c>
     </row>
-    <row r="612" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>234</v>
       </c>
@@ -50461,7 +50460,7 @@
         <v>3692.25</v>
       </c>
     </row>
-    <row r="613" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>238</v>
       </c>
@@ -50534,7 +50533,7 @@
         <v>94.444444444444443</v>
       </c>
     </row>
-    <row r="614" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>238</v>
       </c>
@@ -50611,7 +50610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="615" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>238</v>
       </c>
@@ -50688,7 +50687,7 @@
         <v>83.33</v>
       </c>
     </row>
-    <row r="616" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>238</v>
       </c>
@@ -50765,7 +50764,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="617" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>238</v>
       </c>
@@ -50842,7 +50841,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="618" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>238</v>
       </c>
@@ -50919,7 +50918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="619" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>238</v>
       </c>
@@ -50996,7 +50995,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="620" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>238</v>
       </c>
@@ -51073,7 +51072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="621" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>238</v>
       </c>
@@ -51150,7 +51149,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="622" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>240</v>
       </c>
@@ -51225,7 +51224,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="623" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>251</v>
       </c>
@@ -51300,7 +51299,7 @@
       </c>
       <c r="Y623" s="3"/>
     </row>
-    <row r="624" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>254</v>
       </c>
@@ -51356,7 +51355,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="625" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>263</v>
       </c>
@@ -51433,7 +51432,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="626" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>265</v>
       </c>
@@ -51510,7 +51509,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="627" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>266</v>
       </c>
@@ -51587,7 +51586,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="628" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>300</v>
       </c>
@@ -51664,7 +51663,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="629" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>301</v>
       </c>
@@ -51741,7 +51740,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="630" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>306</v>
       </c>
@@ -51816,7 +51815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>306</v>
       </c>
@@ -51893,7 +51892,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="632" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>306</v>
       </c>
@@ -51970,7 +51969,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="633" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>306</v>
       </c>
@@ -52047,7 +52046,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="634" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>306</v>
       </c>
@@ -52124,7 +52123,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="635" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>306</v>
       </c>
@@ -52201,7 +52200,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="636" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>306</v>
       </c>
@@ -52278,7 +52277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="637" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>347</v>
       </c>
@@ -52355,7 +52354,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="638" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>348</v>
       </c>
@@ -52432,7 +52431,7 @@
         <v>99.936143039591002</v>
       </c>
     </row>
-    <row r="639" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>351</v>
       </c>
@@ -52507,7 +52506,7 @@
         <v>11.41868512110727</v>
       </c>
     </row>
-    <row r="640" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>352</v>
       </c>
@@ -52582,7 +52581,7 @@
         <v>1.0385968556480199E-2</v>
       </c>
     </row>
-    <row r="641" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>368</v>
       </c>
@@ -52655,7 +52654,7 @@
       <c r="X641" s="3"/>
       <c r="Y641" s="3"/>
     </row>
-    <row r="642" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>372</v>
       </c>
@@ -52728,7 +52727,7 @@
       <c r="X642" s="3"/>
       <c r="Y642" s="3"/>
     </row>
-    <row r="643" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>373</v>
       </c>
@@ -52805,7 +52804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>373</v>
       </c>
@@ -52882,7 +52881,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="645" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>373</v>
       </c>
@@ -52959,7 +52958,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="646" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>373</v>
       </c>
@@ -53036,7 +53035,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="647" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>373</v>
       </c>
@@ -53113,7 +53112,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>373</v>
       </c>
@@ -53190,7 +53189,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="649" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>373</v>
       </c>
@@ -53267,7 +53266,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="650" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>390</v>
       </c>
@@ -53344,7 +53343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="651" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>390</v>
       </c>
@@ -53421,7 +53420,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="652" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>390</v>
       </c>
@@ -53498,7 +53497,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="653" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>390</v>
       </c>
@@ -53575,7 +53574,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="654" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>390</v>
       </c>
@@ -53652,7 +53651,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="655" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>390</v>
       </c>
@@ -53729,7 +53728,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="656" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>390</v>
       </c>
@@ -53806,7 +53805,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="657" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>390</v>
       </c>
@@ -53883,7 +53882,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="658" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>390</v>
       </c>
@@ -53960,7 +53959,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="659" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>390</v>
       </c>
@@ -54037,7 +54036,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="660" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>390</v>
       </c>
@@ -54114,7 +54113,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="661" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>390</v>
       </c>
@@ -54191,7 +54190,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="662" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>390</v>
       </c>
@@ -54268,7 +54267,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="663" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>394</v>
       </c>
@@ -54345,7 +54344,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="664" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>395</v>
       </c>
@@ -54420,7 +54419,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="665" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>409</v>
       </c>
@@ -54491,7 +54490,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="666" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="666" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>409</v>
       </c>
@@ -54568,7 +54567,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="667" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="667" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>409</v>
       </c>
@@ -54645,7 +54644,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="668" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>414</v>
       </c>
@@ -54722,7 +54721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="669" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>414</v>
       </c>
@@ -54799,7 +54798,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="670" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>414</v>
       </c>
@@ -54876,7 +54875,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="671" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>414</v>
       </c>
@@ -54953,7 +54952,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="672" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>414</v>
       </c>
@@ -55030,7 +55029,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="673" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>414</v>
       </c>
@@ -55107,7 +55106,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="674" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>414</v>
       </c>
@@ -55184,7 +55183,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="675" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>414</v>
       </c>
@@ -55261,7 +55260,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="676" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>414</v>
       </c>
@@ -55338,7 +55337,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="677" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>414</v>
       </c>
@@ -55415,7 +55414,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="678" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>415</v>
       </c>
@@ -55492,7 +55491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="679" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>415</v>
       </c>
@@ -55569,7 +55568,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="680" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>415</v>
       </c>
@@ -55646,7 +55645,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="681" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>415</v>
       </c>
@@ -55723,7 +55722,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="682" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>415</v>
       </c>
@@ -55800,7 +55799,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="683" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>415</v>
       </c>
@@ -55877,7 +55876,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="684" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>415</v>
       </c>
@@ -55954,7 +55953,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="685" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>415</v>
       </c>
@@ -56031,7 +56030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="686" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>415</v>
       </c>
@@ -56108,7 +56107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="687" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>415</v>
       </c>
@@ -56185,7 +56184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="688" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>415</v>
       </c>
@@ -56262,7 +56261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="689" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>415</v>
       </c>
@@ -56339,7 +56338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="690" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>415</v>
       </c>
@@ -56416,7 +56415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="691" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>415</v>
       </c>
@@ -56493,7 +56492,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="692" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>415</v>
       </c>
@@ -56570,7 +56569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="693" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>416</v>
       </c>
@@ -56647,7 +56646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="694" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>416</v>
       </c>
@@ -56724,7 +56723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="695" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>416</v>
       </c>
@@ -56801,7 +56800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="696" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>416</v>
       </c>
@@ -56878,7 +56877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="697" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>416</v>
       </c>
@@ -56955,7 +56954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="698" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>416</v>
       </c>
@@ -57032,7 +57031,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="699" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>416</v>
       </c>
@@ -57109,7 +57108,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="700" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>417</v>
       </c>
@@ -57186,7 +57185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>417</v>
       </c>
@@ -57263,7 +57262,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="702" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>417</v>
       </c>
@@ -57340,7 +57339,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="703" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>417</v>
       </c>
@@ -57417,7 +57416,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="704" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>417</v>
       </c>
@@ -57494,7 +57493,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="705" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>417</v>
       </c>
@@ -57571,7 +57570,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="706" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>417</v>
       </c>
@@ -57648,7 +57647,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="707" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>418</v>
       </c>
@@ -57725,7 +57724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="708" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>418</v>
       </c>
@@ -57802,7 +57801,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="709" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>418</v>
       </c>
@@ -57879,7 +57878,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="710" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>418</v>
       </c>
@@ -57956,7 +57955,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="711" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>418</v>
       </c>
@@ -58031,7 +58030,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="712" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>418</v>
       </c>
@@ -58108,7 +58107,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="713" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>418</v>
       </c>
@@ -58185,7 +58184,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="714" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>418</v>
       </c>
@@ -58262,7 +58261,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="715" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>418</v>
       </c>
@@ -58339,7 +58338,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="716" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>418</v>
       </c>
@@ -58416,7 +58415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="717" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>420</v>
       </c>
@@ -58493,7 +58492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="718" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>420</v>
       </c>
@@ -58570,7 +58569,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="719" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>420</v>
       </c>
@@ -58647,7 +58646,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="720" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>420</v>
       </c>
@@ -58724,7 +58723,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="721" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>420</v>
       </c>
@@ -58801,7 +58800,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="722" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>420</v>
       </c>
@@ -58878,7 +58877,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="723" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>420</v>
       </c>
@@ -58955,7 +58954,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="724" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="724" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>431</v>
       </c>
@@ -59028,7 +59027,7 @@
       <c r="X724" s="3"/>
       <c r="Y724" s="3"/>
     </row>
-    <row r="725" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>432</v>
       </c>
@@ -59105,7 +59104,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="726" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>432</v>
       </c>
@@ -59182,7 +59181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="727" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="727" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>432</v>
       </c>
@@ -59259,7 +59258,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="728" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>432</v>
       </c>
@@ -59336,7 +59335,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="729" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>432</v>
       </c>
@@ -59413,7 +59412,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="730" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>432</v>
       </c>
@@ -59490,7 +59489,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="731" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>432</v>
       </c>
@@ -59567,7 +59566,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="732" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A732">
         <v>432</v>
       </c>
@@ -59644,7 +59643,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="733" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A733">
         <v>432</v>
       </c>
@@ -59721,7 +59720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="734" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A734">
         <v>432</v>
       </c>
@@ -59798,7 +59797,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="735" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>453</v>
       </c>
@@ -59867,7 +59866,7 @@
       <c r="X735" s="3"/>
       <c r="Y735" s="3"/>
     </row>
-    <row r="736" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>455</v>
       </c>
@@ -59932,7 +59931,7 @@
       <c r="X736" s="3"/>
       <c r="Y736" s="3"/>
     </row>
-    <row r="737" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>456</v>
       </c>
@@ -60003,7 +60002,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="738" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A738">
         <v>456</v>
       </c>
@@ -60080,7 +60079,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="739" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A739">
         <v>456</v>
       </c>
@@ -60157,7 +60156,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="740" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A740">
         <v>456</v>
       </c>
@@ -60234,7 +60233,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="741" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>457</v>
       </c>
@@ -60305,7 +60304,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="742" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A742">
         <v>457</v>
       </c>
@@ -60382,7 +60381,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="743" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A743">
         <v>457</v>
       </c>
@@ -60459,7 +60458,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="744" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A744">
         <v>457</v>
       </c>
@@ -60536,7 +60535,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="745" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>469</v>
       </c>
@@ -60611,7 +60610,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="746" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A746">
         <v>469</v>
       </c>
@@ -60688,7 +60687,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="747" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A747">
         <v>469</v>
       </c>
@@ -60765,7 +60764,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="748" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A748">
         <v>469</v>
       </c>
@@ -60842,7 +60841,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="749" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A749">
         <v>469</v>
       </c>
@@ -60919,7 +60918,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="750" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A750">
         <v>469</v>
       </c>
@@ -60996,7 +60995,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="751" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A751">
         <v>469</v>
       </c>
@@ -61073,7 +61072,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="752" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A752">
         <v>469</v>
       </c>
@@ -61150,7 +61149,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="753" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A753">
         <v>469</v>
       </c>
@@ -61227,7 +61226,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="754" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A754">
         <v>469</v>
       </c>
@@ -61304,7 +61303,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="755" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A755">
         <v>469</v>
       </c>
@@ -61381,7 +61380,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="756" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>470</v>
       </c>
@@ -61458,7 +61457,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="757" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A757">
         <v>470</v>
       </c>
@@ -61533,7 +61532,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="758" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A758">
         <v>470</v>
       </c>
@@ -61610,7 +61609,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="759" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A759">
         <v>470</v>
       </c>
@@ -61687,7 +61686,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="760" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A760">
         <v>470</v>
       </c>
@@ -61764,7 +61763,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="761" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A761">
         <v>470</v>
       </c>
@@ -61841,7 +61840,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="762" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>471</v>
       </c>
@@ -61918,7 +61917,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="763" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A763">
         <v>471</v>
       </c>
@@ -61995,7 +61994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="764" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A764">
         <v>471</v>
       </c>
@@ -62072,7 +62071,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="765" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A765">
         <v>471</v>
       </c>
@@ -62149,7 +62148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="766" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A766">
         <v>471</v>
       </c>
@@ -62226,7 +62225,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="767" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A767">
         <v>471</v>
       </c>
@@ -62303,7 +62302,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="768" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A768">
         <v>471</v>
       </c>
@@ -62380,7 +62379,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="769" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A769">
         <v>471</v>
       </c>
@@ -62457,7 +62456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="770" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>484</v>
       </c>
@@ -62524,7 +62523,7 @@
       <c r="X770" s="3"/>
       <c r="Y770" s="3"/>
     </row>
-    <row r="771" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>510</v>
       </c>
@@ -62599,7 +62598,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="772" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A772">
         <v>510</v>
       </c>
@@ -62670,7 +62669,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="773" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>511</v>
       </c>
@@ -62745,7 +62744,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="774" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="774" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A774">
         <v>511</v>
       </c>
@@ -62822,7 +62821,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="775" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A775">
         <v>511</v>
       </c>
@@ -62899,7 +62898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="776" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A776">
         <v>511</v>
       </c>
@@ -62976,7 +62975,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="777" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A777">
         <v>511</v>
       </c>
@@ -63053,7 +63052,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="778" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A778">
         <v>511</v>
       </c>
@@ -63130,7 +63129,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="779" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A779">
         <v>511</v>
       </c>
@@ -63207,7 +63206,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="780" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A780">
         <v>511</v>
       </c>
@@ -63284,7 +63283,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="781" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="781" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>513</v>
       </c>
@@ -63345,7 +63344,7 @@
       <c r="X781" s="3"/>
       <c r="Y781" s="3"/>
     </row>
-    <row r="782" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>518</v>
       </c>
@@ -63399,7 +63398,7 @@
       </c>
       <c r="R782" s="3"/>
     </row>
-    <row r="783" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>526</v>
       </c>
@@ -63456,7 +63455,7 @@
       <c r="X783" s="3"/>
       <c r="Y783" s="3"/>
     </row>
-    <row r="784" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>529</v>
       </c>
@@ -63531,7 +63530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="785" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A785">
         <v>529</v>
       </c>
@@ -63608,7 +63607,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="786" spans="1:25" hidden="1" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A786">
         <v>529</v>
       </c>
@@ -63687,13 +63686,7 @@
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
-  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="495"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:Y786" xr:uid="{69DEF77A-E506-4471-8935-B3BC88D629C9}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>
